--- a/models-src/oah-models-and-maps.xlsx
+++ b/models-src/oah-models-and-maps.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29628"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workspace\oah\models-src\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F77FB2D5-D379-46D7-A3F6-8BA95B1896C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4561212D-6D29-488F-857E-9D760D31EABF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-90" yWindow="-21710" windowWidth="38620" windowHeight="21100" activeTab="2" xr2:uid="{FA01C668-562A-4AF9-BDB0-B212F14DE883}"/>
+    <workbookView xWindow="-6510" yWindow="-21710" windowWidth="38620" windowHeight="21100" activeTab="2" xr2:uid="{FA01C668-562A-4AF9-BDB0-B212F14DE883}"/>
   </bookViews>
   <sheets>
     <sheet name="ConceptMaps" sheetId="17" r:id="rId1"/>
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1451" uniqueCount="493">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1655" uniqueCount="564">
   <si>
     <t>Group Source</t>
   </si>
@@ -1535,13 +1535,229 @@
   </si>
   <si>
     <t>http://hl7.eu/fhir/ig/oah/StructureDefinition/group-oah</t>
+  </si>
+  <si>
+    <t>causesOfDeath</t>
+  </si>
+  <si>
+    <t>causesOfDeath.tbc</t>
+  </si>
+  <si>
+    <t>causesOfDeath.viralHepatitis</t>
+  </si>
+  <si>
+    <t>causesOfDeath.infectiveAndParasitic</t>
+  </si>
+  <si>
+    <t>causesOfDeath.bloodAndHematopoieticOrgans</t>
+  </si>
+  <si>
+    <t>causesOfDeath.diabetesMellitus</t>
+  </si>
+  <si>
+    <t>causesOfDeath.endocrineNutritionalMetabolic</t>
+  </si>
+  <si>
+    <t>causesOfDeath.ischemicHeart</t>
+  </si>
+  <si>
+    <t>causesOfDeath.otherHeart</t>
+  </si>
+  <si>
+    <t xml:space="preserve">causesOfDeath.otherCirculatorySystem </t>
+  </si>
+  <si>
+    <t>causesOfDeath.pneumonia</t>
+  </si>
+  <si>
+    <t>causesOfDeath.chronicLowerRespiratory</t>
+  </si>
+  <si>
+    <t>causesOfDeath.otherRespiratorySystem</t>
+  </si>
+  <si>
+    <t>causesOfDeath.SkinSubcutaneousTissue</t>
+  </si>
+  <si>
+    <t>causesOfDeath.accidentalPoisoning</t>
+  </si>
+  <si>
+    <t>% of deaths due to TBC</t>
+  </si>
+  <si>
+    <t>% of deaths due to Viral Hepatitis</t>
+  </si>
+  <si>
+    <t>% of deaths due to infective and parasitic diseases</t>
+  </si>
+  <si>
+    <t>% of deaths due to diseases of the blood and hematopoietic organs</t>
+  </si>
+  <si>
+    <t>% of deaths due to Diabetes Mellitus</t>
+  </si>
+  <si>
+    <t>% of deaths due to endocrine, nutritional and metabolic diseases</t>
+  </si>
+  <si>
+    <t>% of deaths due to ischemic diseases of the heart</t>
+  </si>
+  <si>
+    <t>% of deaths due to other diseases of the heart</t>
+  </si>
+  <si>
+    <t xml:space="preserve">% of deaths due to other diseases of the circulatory system </t>
+  </si>
+  <si>
+    <t>% of deaths due to Pneumonia</t>
+  </si>
+  <si>
+    <t>% of deaths due to chronic diseases of the lower respiratory tract</t>
+  </si>
+  <si>
+    <t>% of deaths due to other diseases of the respiratory system</t>
+  </si>
+  <si>
+    <t>% of deaths due to diseases of the skin and subcutaneous tissue</t>
+  </si>
+  <si>
+    <t>% of deaths due to accidental poisoning</t>
+  </si>
+  <si>
+    <t>% of deaths due to cancer</t>
+  </si>
+  <si>
+    <t>% of deaths due to cardiovascular disease</t>
+  </si>
+  <si>
+    <t>% of deaths due to respiratory disease</t>
+  </si>
+  <si>
+    <t>% of deaths due to COPD and lung cancer</t>
+  </si>
+  <si>
+    <t>% of deaths due to all causes</t>
+  </si>
+  <si>
+    <t>% of deaths due to diabetes</t>
+  </si>
+  <si>
+    <t>% of deaths due to Malignant Tumors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">% of deaths due to Healthcare-Sensitive Causes </t>
+  </si>
+  <si>
+    <t>% of Excess Mortality in Winter</t>
+  </si>
+  <si>
+    <t>causesOfDeath.malignantTumor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">causesOfDeath.healthcareSensitiveCauses </t>
+  </si>
+  <si>
+    <t>causesOfDeath.winterExcess</t>
+  </si>
+  <si>
+    <t>causesOfDeath.all</t>
+  </si>
+  <si>
+    <t>causesOfDeath.cancer</t>
+  </si>
+  <si>
+    <t>causesOfDeath.diabetes</t>
+  </si>
+  <si>
+    <t>causesOfDeath.COPDLungCancer</t>
+  </si>
+  <si>
+    <t>Cases of death</t>
+  </si>
+  <si>
+    <t>Cases of death per 100.000 inhabitants, per district, for each of the causes considered as relatable to the project</t>
+  </si>
+  <si>
+    <t>% of hospitalizations due to Diabetes Mellitus</t>
+  </si>
+  <si>
+    <t xml:space="preserve">% of hospitalizations due to Diabetes Mellitus (No. per 100,000 inhabitants) </t>
+  </si>
+  <si>
+    <t>% of hospitalizations due to malignant tumors</t>
+  </si>
+  <si>
+    <t xml:space="preserve">% of hospitalizations due to malignant tumors (number per 100,000 inhabitants) 
+</t>
+  </si>
+  <si>
+    <t>% of hospitalizations due to Hypertension</t>
+  </si>
+  <si>
+    <t xml:space="preserve">% of hospitalizations due to Hypertension (No. per 100,000 inhabitants) </t>
+  </si>
+  <si>
+    <t>% of hospitalizations due to Circulatory System Diseases</t>
+  </si>
+  <si>
+    <t xml:space="preserve">% of hospitalizations due to Circulatory System Diseases (No. per 100,000 inhabitants) </t>
+  </si>
+  <si>
+    <t>% of hospitalizations due to respiratory diseases</t>
+  </si>
+  <si>
+    <t xml:space="preserve">% of hospitalizations due to respiratory diseases (No. per 100,000 inhabitants) </t>
+  </si>
+  <si>
+    <t>% of hospitalizations for Asthma</t>
+  </si>
+  <si>
+    <t xml:space="preserve">% of hospitalizations for Asthma (No. per 100,000 inhabitants) </t>
+  </si>
+  <si>
+    <t xml:space="preserve">% of hospitalizations avoidable by primary prevention
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">% of hospitalizations avoidable by primary prevention (No. per 100,000 inhabitants) 
+</t>
+  </si>
+  <si>
+    <t>hospitalization</t>
+  </si>
+  <si>
+    <t>causesOfDeath.cardiovascular</t>
+  </si>
+  <si>
+    <t>causesOfDeath.respiratory</t>
+  </si>
+  <si>
+    <t>hospitalization.diabetesMellitus</t>
+  </si>
+  <si>
+    <t>hospitalization.malignantTumor</t>
+  </si>
+  <si>
+    <t>hospitalization.cardiovascular</t>
+  </si>
+  <si>
+    <t>hospitalization.respiratory</t>
+  </si>
+  <si>
+    <t>hospitalization.hypertension</t>
+  </si>
+  <si>
+    <t>hospitalization.asthma</t>
+  </si>
+  <si>
+    <t>hospitalization.avoidablePrimaryPrevention</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1599,8 +1815,41 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
   </fonts>
-  <fills count="9">
+  <fills count="13">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1646,6 +1895,30 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="2" tint="-9.9978637043366805E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1711,15 +1984,17 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="top"/>
       <protection locked="0"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="63">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1831,11 +2106,37 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="4" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="3" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="4" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="12" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
-  <cellStyles count="3">
+  <cellStyles count="5">
     <cellStyle name="Collegamento ipertestuale" xfId="1" builtinId="8"/>
     <cellStyle name="Collegamento ipertestuale 2" xfId="2" xr:uid="{2FCB844D-8848-4EB2-8C88-A6D12B4D0B5A}"/>
     <cellStyle name="Normale" xfId="0" builtinId="0"/>
+    <cellStyle name="Normale 2 2" xfId="3" xr:uid="{4D65F763-B5AF-4AB8-93D2-357F01C3F710}"/>
+    <cellStyle name="Normale 3" xfId="4" xr:uid="{847AE9A0-1614-4FE4-A0CF-6F1B7AAADF24}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -2223,20 +2524,20 @@
     <tabColor theme="7" tint="0.59999389629810485"/>
   </sheetPr>
   <dimension ref="A1:AZ26"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="31.453125" customWidth="1"/>
-    <col min="2" max="2" width="29.453125" customWidth="1"/>
-    <col min="3" max="3" width="56.54296875" customWidth="1"/>
-    <col min="4" max="4" width="38.76953125" style="5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="52.31640625" style="5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="31.46484375" customWidth="1"/>
+    <col min="2" max="2" width="29.46484375" customWidth="1"/>
+    <col min="3" max="3" width="56.53125" customWidth="1"/>
+    <col min="4" max="4" width="38.796875" style="5" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="52.33203125" style="5" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="6" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.54296875" customWidth="1"/>
-    <col min="8" max="8" width="12.54296875" customWidth="1"/>
-    <col min="9" max="9" width="13.76953125" customWidth="1"/>
+    <col min="7" max="7" width="15.53125" customWidth="1"/>
+    <col min="8" max="8" width="12.53125" customWidth="1"/>
+    <col min="9" max="9" width="13.796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:52" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:52" x14ac:dyDescent="0.45">
       <c r="A1" s="2" t="s">
         <v>15</v>
       </c>
@@ -2265,7 +2566,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="2" spans="1:52" x14ac:dyDescent="0.75">
+    <row r="2" spans="1:52" x14ac:dyDescent="0.45">
       <c r="A2" s="6" t="s">
         <v>104</v>
       </c>
@@ -2291,7 +2592,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="3" spans="1:52" s="6" customFormat="1" ht="29.5" x14ac:dyDescent="0.75">
+    <row r="3" spans="1:52" s="6" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A3" s="6" t="s">
         <v>201</v>
       </c>
@@ -2356,7 +2657,7 @@
       <c r="AY3"/>
       <c r="AZ3"/>
     </row>
-    <row r="4" spans="1:52" s="6" customFormat="1" ht="29.5" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:52" s="6" customFormat="1" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A4" s="6" t="s">
         <v>208</v>
       </c>
@@ -2421,7 +2722,7 @@
       <c r="AY4"/>
       <c r="AZ4"/>
     </row>
-    <row r="5" spans="1:52" s="6" customFormat="1" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:52" s="6" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A5" s="6" t="s">
         <v>312</v>
       </c>
@@ -2486,7 +2787,7 @@
       <c r="AY5"/>
       <c r="AZ5"/>
     </row>
-    <row r="6" spans="1:52" s="6" customFormat="1" x14ac:dyDescent="0.75">
+    <row r="6" spans="1:52" s="6" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A6" s="6" t="s">
         <v>296</v>
       </c>
@@ -2551,7 +2852,7 @@
       <c r="AY6"/>
       <c r="AZ6"/>
     </row>
-    <row r="7" spans="1:52" s="6" customFormat="1" x14ac:dyDescent="0.75">
+    <row r="7" spans="1:52" s="6" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A7" s="6" t="s">
         <v>471</v>
       </c>
@@ -2616,7 +2917,7 @@
       <c r="AY7"/>
       <c r="AZ7"/>
     </row>
-    <row r="8" spans="1:52" x14ac:dyDescent="0.75">
+    <row r="8" spans="1:52" x14ac:dyDescent="0.45">
       <c r="A8" s="6" t="s">
         <v>488</v>
       </c>
@@ -2640,7 +2941,7 @@
       <c r="H8" s="10"/>
       <c r="I8" s="6"/>
     </row>
-    <row r="9" spans="1:52" x14ac:dyDescent="0.75">
+    <row r="9" spans="1:52" x14ac:dyDescent="0.45">
       <c r="A9" s="6"/>
       <c r="B9" s="7"/>
       <c r="C9" s="7"/>
@@ -2651,7 +2952,7 @@
       <c r="H9" s="10"/>
       <c r="I9" s="6"/>
     </row>
-    <row r="10" spans="1:52" x14ac:dyDescent="0.75">
+    <row r="10" spans="1:52" x14ac:dyDescent="0.45">
       <c r="A10" s="6"/>
       <c r="B10" s="7"/>
       <c r="C10" s="7"/>
@@ -2662,7 +2963,7 @@
       <c r="H10" s="10"/>
       <c r="I10" s="6"/>
     </row>
-    <row r="11" spans="1:52" x14ac:dyDescent="0.75">
+    <row r="11" spans="1:52" x14ac:dyDescent="0.45">
       <c r="A11" s="9"/>
       <c r="B11" s="7"/>
       <c r="C11" s="7"/>
@@ -2673,7 +2974,7 @@
       <c r="H11" s="10"/>
       <c r="I11" s="6"/>
     </row>
-    <row r="12" spans="1:52" x14ac:dyDescent="0.75">
+    <row r="12" spans="1:52" x14ac:dyDescent="0.45">
       <c r="A12" s="9"/>
       <c r="B12" s="7"/>
       <c r="C12" s="7"/>
@@ -2684,7 +2985,7 @@
       <c r="H12" s="6"/>
       <c r="I12" s="6"/>
     </row>
-    <row r="13" spans="1:52" x14ac:dyDescent="0.75">
+    <row r="13" spans="1:52" x14ac:dyDescent="0.45">
       <c r="A13" s="6"/>
       <c r="B13" s="7"/>
       <c r="C13" s="7"/>
@@ -2695,7 +2996,7 @@
       <c r="H13" s="6"/>
       <c r="I13" s="6"/>
     </row>
-    <row r="14" spans="1:52" x14ac:dyDescent="0.75">
+    <row r="14" spans="1:52" x14ac:dyDescent="0.45">
       <c r="A14" s="6"/>
       <c r="B14" s="7"/>
       <c r="C14" s="7"/>
@@ -2706,10 +3007,10 @@
       <c r="H14" s="6"/>
       <c r="I14" s="6"/>
     </row>
-    <row r="16" spans="1:52" x14ac:dyDescent="0.75">
+    <row r="16" spans="1:52" x14ac:dyDescent="0.45">
       <c r="A16" s="1"/>
     </row>
-    <row r="26" spans="3:3" x14ac:dyDescent="0.75">
+    <row r="26" spans="3:3" x14ac:dyDescent="0.45">
       <c r="C26" s="3"/>
     </row>
   </sheetData>
@@ -2738,16 +3039,16 @@
     <tabColor theme="6" tint="0.79998168889431442"/>
   </sheetPr>
   <dimension ref="A1:E6"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="20.453125" customWidth="1"/>
-    <col min="2" max="2" width="11.54296875" customWidth="1"/>
+    <col min="1" max="1" width="20.46484375" customWidth="1"/>
+    <col min="2" max="2" width="11.53125" customWidth="1"/>
     <col min="3" max="3" width="33" customWidth="1"/>
-    <col min="4" max="4" width="23.31640625" customWidth="1"/>
-    <col min="5" max="5" width="35.08984375" customWidth="1"/>
+    <col min="4" max="4" width="23.33203125" customWidth="1"/>
+    <col min="5" max="5" width="35.06640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A1" s="16" t="s">
         <v>9</v>
       </c>
@@ -2764,7 +3065,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="29.5" x14ac:dyDescent="0.75">
+    <row r="2" spans="1:5" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A2" s="6" t="s">
         <v>122</v>
       </c>
@@ -2781,7 +3082,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="29.5" x14ac:dyDescent="0.75">
+    <row r="3" spans="1:5" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A3" s="6" t="s">
         <v>141</v>
       </c>
@@ -2798,7 +3099,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A4" s="6" t="s">
         <v>106</v>
       </c>
@@ -2815,7 +3116,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A5" s="6" t="s">
         <v>151</v>
       </c>
@@ -2832,7 +3133,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="29.5" x14ac:dyDescent="0.75">
+    <row r="6" spans="1:5" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A6" s="6" t="s">
         <v>149</v>
       </c>
@@ -2860,19 +3161,19 @@
     <tabColor theme="7" tint="0.59999389629810485"/>
   </sheetPr>
   <dimension ref="A1:H10"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="58.08984375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="58.06640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="71.86328125" customWidth="1"/>
-    <col min="3" max="3" width="76.76953125" style="5" customWidth="1"/>
-    <col min="4" max="4" width="44.54296875" style="5" customWidth="1"/>
-    <col min="5" max="5" width="36.2265625" customWidth="1"/>
+    <col min="3" max="3" width="76.796875" style="5" customWidth="1"/>
+    <col min="4" max="4" width="44.53125" style="5" customWidth="1"/>
+    <col min="5" max="5" width="36.19921875" customWidth="1"/>
     <col min="6" max="6" width="22" customWidth="1"/>
-    <col min="7" max="7" width="11.08984375" customWidth="1"/>
-    <col min="8" max="8" width="37.54296875" style="5" customWidth="1"/>
+    <col min="7" max="7" width="11.06640625" customWidth="1"/>
+    <col min="8" max="8" width="37.53125" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="14" customFormat="1" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:8" s="14" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
@@ -2898,7 +3199,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="29.5" x14ac:dyDescent="0.75">
+    <row r="2" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A2" s="7" t="str">
         <f>"http://hl7.eu/fhir/ig/oah/StructureDefinition/"&amp;LogicalModels!$A$4</f>
         <v>http://hl7.eu/fhir/ig/oah/StructureDefinition/StructuredIndicator</v>
@@ -2925,7 +3226,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.75">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A3" s="7" t="str">
         <f>"http://hl7.eu/fhir/ig/oah/StructureDefinition/"&amp;LogicalModels!$A$4</f>
         <v>http://hl7.eu/fhir/ig/oah/StructureDefinition/StructuredIndicator</v>
@@ -2950,7 +3251,7 @@
       </c>
       <c r="H3" s="8"/>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A4" s="7" t="str">
         <f>"http://hl7.eu/fhir/ig/oah/StructureDefinition/"&amp;LogicalModels!$A$4</f>
         <v>http://hl7.eu/fhir/ig/oah/StructureDefinition/StructuredIndicator</v>
@@ -2978,7 +3279,7 @@
       </c>
       <c r="H4" s="8"/>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A5" s="7" t="str">
         <f>"http://hl7.eu/fhir/ig/oah/StructureDefinition/"&amp;LogicalModels!$A$4</f>
         <v>http://hl7.eu/fhir/ig/oah/StructureDefinition/StructuredIndicator</v>
@@ -3006,7 +3307,7 @@
       </c>
       <c r="H5" s="8"/>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.75">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A6" s="7" t="str">
         <f>"http://hl7.eu/fhir/ig/oah/StructureDefinition/"&amp;LogicalModels!$A$4</f>
         <v>http://hl7.eu/fhir/ig/oah/StructureDefinition/StructuredIndicator</v>
@@ -3031,7 +3332,7 @@
       </c>
       <c r="H6" s="8"/>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.75">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A7" s="7" t="str">
         <f>"http://hl7.eu/fhir/ig/oah/StructureDefinition/"&amp;LogicalModels!$A$4</f>
         <v>http://hl7.eu/fhir/ig/oah/StructureDefinition/StructuredIndicator</v>
@@ -3058,7 +3359,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.75">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A8" s="7" t="str">
         <f>"http://hl7.eu/fhir/ig/oah/StructureDefinition/"&amp;LogicalModels!$A$4</f>
         <v>http://hl7.eu/fhir/ig/oah/StructureDefinition/StructuredIndicator</v>
@@ -3083,7 +3384,7 @@
       </c>
       <c r="H8" s="8"/>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.75">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A9" s="7" t="str">
         <f>"http://hl7.eu/fhir/ig/oah/StructureDefinition/"&amp;LogicalModels!$A$4</f>
         <v>http://hl7.eu/fhir/ig/oah/StructureDefinition/StructuredIndicator</v>
@@ -3108,7 +3409,7 @@
       </c>
       <c r="H9" s="8"/>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.75">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A10" s="7" t="str">
         <f>"http://hl7.eu/fhir/ig/oah/StructureDefinition/"&amp;LogicalModels!$A$4</f>
         <v>http://hl7.eu/fhir/ig/oah/StructureDefinition/StructuredIndicator</v>
@@ -3148,16 +3449,16 @@
     <tabColor theme="6" tint="0.79998168889431442"/>
   </sheetPr>
   <dimension ref="A1:E8"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="36" customWidth="1"/>
-    <col min="2" max="2" width="11.54296875" customWidth="1"/>
-    <col min="3" max="3" width="36.2265625" customWidth="1"/>
-    <col min="4" max="4" width="39.6796875" customWidth="1"/>
-    <col min="5" max="5" width="35.08984375" customWidth="1"/>
+    <col min="2" max="2" width="11.53125" customWidth="1"/>
+    <col min="3" max="3" width="36.19921875" customWidth="1"/>
+    <col min="4" max="4" width="39.6640625" customWidth="1"/>
+    <col min="5" max="5" width="35.06640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A1" s="16" t="s">
         <v>9</v>
       </c>
@@ -3174,7 +3475,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="29.5" x14ac:dyDescent="0.75">
+    <row r="2" spans="1:5" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A2" s="6" t="s">
         <v>122</v>
       </c>
@@ -3191,7 +3492,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="29.5" x14ac:dyDescent="0.75">
+    <row r="3" spans="1:5" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A3" s="6" t="s">
         <v>141</v>
       </c>
@@ -3208,7 +3509,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A4" s="6" t="s">
         <v>106</v>
       </c>
@@ -3225,7 +3526,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A5" s="6" t="s">
         <v>151</v>
       </c>
@@ -3242,7 +3543,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A6" s="29" t="s">
         <v>132</v>
       </c>
@@ -3259,7 +3560,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="29.5" x14ac:dyDescent="0.75">
+    <row r="7" spans="1:5" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A7" s="6" t="s">
         <v>145</v>
       </c>
@@ -3276,7 +3577,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="29.5" x14ac:dyDescent="0.75">
+    <row r="8" spans="1:5" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A8" s="6" t="s">
         <v>150</v>
       </c>
@@ -3304,19 +3605,19 @@
     <tabColor theme="7" tint="0.59999389629810485"/>
   </sheetPr>
   <dimension ref="A1:H12"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="58.08984375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="58.06640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="71.86328125" customWidth="1"/>
     <col min="3" max="3" width="36" style="5" customWidth="1"/>
-    <col min="4" max="4" width="44.54296875" style="5" customWidth="1"/>
-    <col min="5" max="5" width="36.2265625" customWidth="1"/>
+    <col min="4" max="4" width="44.53125" style="5" customWidth="1"/>
+    <col min="5" max="5" width="36.19921875" customWidth="1"/>
     <col min="6" max="6" width="22" customWidth="1"/>
-    <col min="7" max="7" width="11.08984375" customWidth="1"/>
-    <col min="8" max="8" width="37.54296875" style="5" customWidth="1"/>
+    <col min="7" max="7" width="11.06640625" customWidth="1"/>
+    <col min="8" max="8" width="37.53125" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="14" customFormat="1" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:8" s="14" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
@@ -3342,7 +3643,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.75">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A2" s="7" t="str">
         <f>"http://hl7.eu/fhir/ig/oah/StructureDefinition/"&amp;LogicalModels!$A$5</f>
         <v>http://hl7.eu/fhir/ig/oah/StructureDefinition/Sample</v>
@@ -3369,7 +3670,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.75">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A3" s="7" t="str">
         <f>"http://hl7.eu/fhir/ig/oah/StructureDefinition/"&amp;LogicalModels!$A$5</f>
         <v>http://hl7.eu/fhir/ig/oah/StructureDefinition/Sample</v>
@@ -3394,7 +3695,7 @@
       </c>
       <c r="H3" s="8"/>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A4" s="7" t="str">
         <f>"http://hl7.eu/fhir/ig/oah/StructureDefinition/"&amp;LogicalModels!$A$5</f>
         <v>http://hl7.eu/fhir/ig/oah/StructureDefinition/Sample</v>
@@ -3419,7 +3720,7 @@
       </c>
       <c r="H4" s="8"/>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A5" s="7" t="str">
         <f>"http://hl7.eu/fhir/ig/oah/StructureDefinition/"&amp;LogicalModels!$A$5</f>
         <v>http://hl7.eu/fhir/ig/oah/StructureDefinition/Sample</v>
@@ -3444,7 +3745,7 @@
       </c>
       <c r="H5" s="8"/>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.75">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A6" s="7" t="str">
         <f>"http://hl7.eu/fhir/ig/oah/StructureDefinition/"&amp;LogicalModels!$A$5</f>
         <v>http://hl7.eu/fhir/ig/oah/StructureDefinition/Sample</v>
@@ -3469,7 +3770,7 @@
       </c>
       <c r="H6" s="8"/>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.75">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A7" s="7" t="str">
         <f>"http://hl7.eu/fhir/ig/oah/StructureDefinition/"&amp;LogicalModels!$A$5</f>
         <v>http://hl7.eu/fhir/ig/oah/StructureDefinition/Sample</v>
@@ -3494,7 +3795,7 @@
       </c>
       <c r="H7" s="8"/>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.75">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A8" s="7" t="str">
         <f>"http://hl7.eu/fhir/ig/oah/StructureDefinition/"&amp;LogicalModels!$A$5</f>
         <v>http://hl7.eu/fhir/ig/oah/StructureDefinition/Sample</v>
@@ -3519,7 +3820,7 @@
       </c>
       <c r="H8" s="8"/>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.75">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A9" s="7" t="str">
         <f>"http://hl7.eu/fhir/ig/oah/StructureDefinition/"&amp;LogicalModels!$A$5</f>
         <v>http://hl7.eu/fhir/ig/oah/StructureDefinition/Sample</v>
@@ -3544,7 +3845,7 @@
       </c>
       <c r="H9" s="8"/>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.75">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A10" s="7" t="str">
         <f>"http://hl7.eu/fhir/ig/oah/StructureDefinition/"&amp;LogicalModels!$A$5</f>
         <v>http://hl7.eu/fhir/ig/oah/StructureDefinition/Sample</v>
@@ -3569,7 +3870,7 @@
       </c>
       <c r="H10" s="8"/>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.75">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A11" s="7" t="str">
         <f>"http://hl7.eu/fhir/ig/oah/StructureDefinition/"&amp;LogicalModels!$A$5</f>
         <v>http://hl7.eu/fhir/ig/oah/StructureDefinition/Sample</v>
@@ -3594,7 +3895,7 @@
       </c>
       <c r="H11" s="8"/>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.75">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A12" s="7" t="str">
         <f>"http://hl7.eu/fhir/ig/oah/StructureDefinition/"&amp;LogicalModels!$A$5</f>
         <v>http://hl7.eu/fhir/ig/oah/StructureDefinition/Sample</v>
@@ -3634,16 +3935,16 @@
     <tabColor theme="6" tint="0.79998168889431442"/>
   </sheetPr>
   <dimension ref="A1:E9"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="35.6796875" customWidth="1"/>
-    <col min="2" max="2" width="11.54296875" customWidth="1"/>
-    <col min="3" max="3" width="36.2265625" customWidth="1"/>
-    <col min="4" max="4" width="39.6796875" customWidth="1"/>
-    <col min="5" max="5" width="35.08984375" customWidth="1"/>
+    <col min="1" max="1" width="35.6640625" customWidth="1"/>
+    <col min="2" max="2" width="11.53125" customWidth="1"/>
+    <col min="3" max="3" width="36.19921875" customWidth="1"/>
+    <col min="4" max="4" width="39.6640625" customWidth="1"/>
+    <col min="5" max="5" width="35.06640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A1" s="16" t="s">
         <v>9</v>
       </c>
@@ -3660,7 +3961,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A2" s="8" t="s">
         <v>107</v>
       </c>
@@ -3677,7 +3978,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A3" s="8" t="s">
         <v>135</v>
       </c>
@@ -3694,7 +3995,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A4" s="8" t="s">
         <v>108</v>
       </c>
@@ -3711,7 +4012,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A5" s="8" t="s">
         <v>109</v>
       </c>
@@ -3728,7 +4029,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A6" s="8" t="s">
         <v>118</v>
       </c>
@@ -3745,7 +4046,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="44.25" x14ac:dyDescent="0.75">
+    <row r="7" spans="1:5" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A7" s="8" t="s">
         <v>136</v>
       </c>
@@ -3762,7 +4063,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A8" s="8" t="s">
         <v>114</v>
       </c>
@@ -3779,7 +4080,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A9" s="8" t="s">
         <v>152</v>
       </c>
@@ -3807,19 +4108,19 @@
     <tabColor theme="7" tint="0.59999389629810485"/>
   </sheetPr>
   <dimension ref="A1:H25"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="58.08984375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="58.06640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="71.86328125" customWidth="1"/>
     <col min="3" max="3" width="36" style="5" customWidth="1"/>
-    <col min="4" max="4" width="44.54296875" style="5" customWidth="1"/>
-    <col min="5" max="5" width="36.2265625" customWidth="1"/>
+    <col min="4" max="4" width="44.53125" style="5" customWidth="1"/>
+    <col min="5" max="5" width="36.19921875" customWidth="1"/>
     <col min="6" max="6" width="22" customWidth="1"/>
-    <col min="7" max="7" width="11.08984375" customWidth="1"/>
-    <col min="8" max="8" width="37.54296875" style="5" customWidth="1"/>
+    <col min="7" max="7" width="11.06640625" customWidth="1"/>
+    <col min="8" max="8" width="37.53125" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="14" customFormat="1" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:8" s="14" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
@@ -3845,7 +4146,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="29.5" x14ac:dyDescent="0.75">
+    <row r="2" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A2" s="7" t="str">
         <f>"http://hl7.eu/fhir/ig/oah/StructureDefinition/"&amp;LogicalModels!$A$6</f>
         <v>http://hl7.eu/fhir/ig/oah/StructureDefinition/DataSet</v>
@@ -3872,7 +4173,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.75">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A3" s="7" t="str">
         <f>"http://hl7.eu/fhir/ig/oah/StructureDefinition/"&amp;LogicalModels!$A$6</f>
         <v>http://hl7.eu/fhir/ig/oah/StructureDefinition/DataSet</v>
@@ -3897,7 +4198,7 @@
       </c>
       <c r="H3" s="8"/>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A4" s="7" t="str">
         <f>"http://hl7.eu/fhir/ig/oah/StructureDefinition/"&amp;LogicalModels!$A$6</f>
         <v>http://hl7.eu/fhir/ig/oah/StructureDefinition/DataSet</v>
@@ -3925,7 +4226,7 @@
       </c>
       <c r="H4" s="8"/>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A5" s="7" t="str">
         <f>"http://hl7.eu/fhir/ig/oah/StructureDefinition/"&amp;LogicalModels!$A$6</f>
         <v>http://hl7.eu/fhir/ig/oah/StructureDefinition/DataSet</v>
@@ -3953,7 +4254,7 @@
       </c>
       <c r="H5" s="8"/>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.75">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A6" s="7" t="str">
         <f>"http://hl7.eu/fhir/ig/oah/StructureDefinition/"&amp;LogicalModels!$A$6</f>
         <v>http://hl7.eu/fhir/ig/oah/StructureDefinition/DataSet</v>
@@ -3978,7 +4279,7 @@
       </c>
       <c r="H6" s="8"/>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.75">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A7" s="7" t="str">
         <f>"http://hl7.eu/fhir/ig/oah/StructureDefinition/"&amp;LogicalModels!$A$6</f>
         <v>http://hl7.eu/fhir/ig/oah/StructureDefinition/DataSet</v>
@@ -4005,7 +4306,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.75">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A8" s="7" t="str">
         <f>"http://hl7.eu/fhir/ig/oah/StructureDefinition/"&amp;LogicalModels!$A$6</f>
         <v>http://hl7.eu/fhir/ig/oah/StructureDefinition/DataSet</v>
@@ -4030,7 +4331,7 @@
       </c>
       <c r="H8" s="8"/>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.75">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A9" s="7" t="str">
         <f>"http://hl7.eu/fhir/ig/oah/StructureDefinition/"&amp;LogicalModels!$A$6</f>
         <v>http://hl7.eu/fhir/ig/oah/StructureDefinition/DataSet</v>
@@ -4053,7 +4354,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.75">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A10" s="7" t="str">
         <f>"http://hl7.eu/fhir/ig/oah/StructureDefinition/"&amp;LogicalModels!$A$6</f>
         <v>http://hl7.eu/fhir/ig/oah/StructureDefinition/DataSet</v>
@@ -4078,7 +4379,7 @@
       </c>
       <c r="H10" s="8"/>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.75">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A11" s="7" t="str">
         <f>"http://hl7.eu/fhir/ig/oah/StructureDefinition/"&amp;LogicalModels!$A$6</f>
         <v>http://hl7.eu/fhir/ig/oah/StructureDefinition/DataSet</v>
@@ -4103,7 +4404,7 @@
       </c>
       <c r="H11" s="8"/>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.75">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A12" s="7" t="str">
         <f>"http://hl7.eu/fhir/ig/oah/StructureDefinition/"&amp;LogicalModels!$A$6</f>
         <v>http://hl7.eu/fhir/ig/oah/StructureDefinition/DataSet</v>
@@ -4128,7 +4429,7 @@
       </c>
       <c r="H12" s="8"/>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.75">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A13" s="7" t="str">
         <f>"http://hl7.eu/fhir/ig/oah/StructureDefinition/"&amp;LogicalModels!$A$6</f>
         <v>http://hl7.eu/fhir/ig/oah/StructureDefinition/DataSet</v>
@@ -4153,7 +4454,7 @@
       </c>
       <c r="H13" s="8"/>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.75">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A14" s="7" t="str">
         <f>"http://hl7.eu/fhir/ig/oah/StructureDefinition/"&amp;LogicalModels!$A$6</f>
         <v>http://hl7.eu/fhir/ig/oah/StructureDefinition/DataSet</v>
@@ -4178,7 +4479,7 @@
       </c>
       <c r="H14" s="8"/>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.75">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A15" s="7" t="str">
         <f>"http://hl7.eu/fhir/ig/oah/StructureDefinition/"&amp;LogicalModels!$A$6</f>
         <v>http://hl7.eu/fhir/ig/oah/StructureDefinition/DataSet</v>
@@ -4203,7 +4504,7 @@
       </c>
       <c r="H15" s="8"/>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.75">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A16" s="7" t="str">
         <f>"http://hl7.eu/fhir/ig/oah/StructureDefinition/"&amp;LogicalModels!$A$6</f>
         <v>http://hl7.eu/fhir/ig/oah/StructureDefinition/DataSet</v>
@@ -4228,7 +4529,7 @@
       </c>
       <c r="H16" s="8"/>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.75">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A17" s="7" t="str">
         <f>"http://hl7.eu/fhir/ig/oah/StructureDefinition/"&amp;LogicalModels!$A$6</f>
         <v>http://hl7.eu/fhir/ig/oah/StructureDefinition/DataSet</v>
@@ -4253,7 +4554,7 @@
       </c>
       <c r="H17" s="8"/>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.75">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A18" s="7" t="str">
         <f>"http://hl7.eu/fhir/ig/oah/StructureDefinition/"&amp;LogicalModels!$A$6</f>
         <v>http://hl7.eu/fhir/ig/oah/StructureDefinition/DataSet</v>
@@ -4278,7 +4579,7 @@
       </c>
       <c r="H18" s="8"/>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.75">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A19" s="7" t="str">
         <f>"http://hl7.eu/fhir/ig/oah/StructureDefinition/"&amp;LogicalModels!$A$6</f>
         <v>http://hl7.eu/fhir/ig/oah/StructureDefinition/DataSet</v>
@@ -4303,7 +4604,7 @@
       </c>
       <c r="H19" s="8"/>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.75">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A20" s="7" t="str">
         <f>"http://hl7.eu/fhir/ig/oah/StructureDefinition/"&amp;LogicalModels!$A$6</f>
         <v>http://hl7.eu/fhir/ig/oah/StructureDefinition/DataSet</v>
@@ -4330,7 +4631,7 @@
         <v>292</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.75">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A21" s="7" t="str">
         <f>"http://hl7.eu/fhir/ig/oah/StructureDefinition/"&amp;LogicalModels!$A$6</f>
         <v>http://hl7.eu/fhir/ig/oah/StructureDefinition/DataSet</v>
@@ -4355,7 +4656,7 @@
       </c>
       <c r="H21" s="8"/>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.75">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A22" s="7" t="str">
         <f>"http://hl7.eu/fhir/ig/oah/StructureDefinition/"&amp;LogicalModels!$A$6</f>
         <v>http://hl7.eu/fhir/ig/oah/StructureDefinition/DataSet</v>
@@ -4380,7 +4681,7 @@
       </c>
       <c r="H22" s="8"/>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.75">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A23" s="7" t="str">
         <f>"http://hl7.eu/fhir/ig/oah/StructureDefinition/"&amp;LogicalModels!$A$6</f>
         <v>http://hl7.eu/fhir/ig/oah/StructureDefinition/DataSet</v>
@@ -4405,7 +4706,7 @@
       </c>
       <c r="H23" s="8"/>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.75">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A24" s="7" t="str">
         <f>"http://hl7.eu/fhir/ig/oah/StructureDefinition/"&amp;LogicalModels!$A$6</f>
         <v>http://hl7.eu/fhir/ig/oah/StructureDefinition/DataSet</v>
@@ -4432,7 +4733,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.75">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A25" s="7" t="str">
         <f>"http://hl7.eu/fhir/ig/oah/StructureDefinition/"&amp;LogicalModels!$A$6</f>
         <v>http://hl7.eu/fhir/ig/oah/StructureDefinition/DataSet</v>
@@ -4494,17 +4795,17 @@
     <tabColor theme="6" tint="0.79998168889431442"/>
   </sheetPr>
   <dimension ref="A1:E21"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="53.86328125" customWidth="1"/>
-    <col min="2" max="2" width="11.54296875" customWidth="1"/>
-    <col min="3" max="3" width="15.76953125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="39.6796875" customWidth="1"/>
-    <col min="5" max="5" width="35.08984375" customWidth="1"/>
-    <col min="6" max="6" width="13.453125" customWidth="1"/>
+    <col min="2" max="2" width="11.53125" customWidth="1"/>
+    <col min="3" max="3" width="15.796875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="39.6640625" customWidth="1"/>
+    <col min="5" max="5" width="35.06640625" customWidth="1"/>
+    <col min="6" max="6" width="13.46484375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A1" s="2" t="s">
         <v>9</v>
       </c>
@@ -4521,7 +4822,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="29.5" x14ac:dyDescent="0.75">
+    <row r="2" spans="1:5" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A2" s="35" t="s">
         <v>250</v>
       </c>
@@ -4538,7 +4839,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A3" s="35" t="s">
         <v>214</v>
       </c>
@@ -4555,7 +4856,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A4" s="35" t="s">
         <v>67</v>
       </c>
@@ -4572,7 +4873,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A5" s="35" t="s">
         <v>219</v>
       </c>
@@ -4589,7 +4890,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A6" s="35" t="s">
         <v>141</v>
       </c>
@@ -4606,7 +4907,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A7" s="35" t="s">
         <v>253</v>
       </c>
@@ -4623,7 +4924,7 @@
         <v>255</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A8" s="35" t="s">
         <v>218</v>
       </c>
@@ -4640,7 +4941,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A9" s="35" t="s">
         <v>212</v>
       </c>
@@ -4657,7 +4958,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="29.5" x14ac:dyDescent="0.75">
+    <row r="10" spans="1:5" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A10" s="35" t="s">
         <v>106</v>
       </c>
@@ -4674,7 +4975,7 @@
         <v>271</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="29.5" x14ac:dyDescent="0.75">
+    <row r="11" spans="1:5" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A11" s="35" t="s">
         <v>275</v>
       </c>
@@ -4691,7 +4992,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="59" x14ac:dyDescent="0.75">
+    <row r="12" spans="1:5" ht="57" x14ac:dyDescent="0.45">
       <c r="A12" s="36" t="s">
         <v>272</v>
       </c>
@@ -4708,7 +5009,7 @@
         <v>274</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A13" s="35" t="s">
         <v>213</v>
       </c>
@@ -4725,7 +5026,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A14" s="35" t="s">
         <v>228</v>
       </c>
@@ -4742,7 +5043,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A15" s="9" t="s">
         <v>105</v>
       </c>
@@ -4759,7 +5060,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A16" s="6" t="s">
         <v>223</v>
       </c>
@@ -4776,7 +5077,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="17" spans="1:5" s="20" customFormat="1" x14ac:dyDescent="0.75">
+    <row r="17" spans="1:5" s="20" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A17" s="35" t="s">
         <v>234</v>
       </c>
@@ -4793,7 +5094,7 @@
         <v>239</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A18" s="34" t="s">
         <v>235</v>
       </c>
@@ -4810,7 +5111,7 @@
         <v>240</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A19" s="34" t="s">
         <v>236</v>
       </c>
@@ -4827,7 +5128,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A20" s="34" t="s">
         <v>237</v>
       </c>
@@ -4844,7 +5145,7 @@
         <v>243</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A21" s="34" t="s">
         <v>238</v>
       </c>
@@ -4870,16 +5171,16 @@
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{06ED8D9E-4C8F-4866-AD65-D95CCFA6E5A0}">
   <dimension ref="A1:E9"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="36" customWidth="1"/>
-    <col min="2" max="2" width="11.54296875" customWidth="1"/>
-    <col min="3" max="3" width="36.2265625" customWidth="1"/>
-    <col min="4" max="4" width="39.6796875" customWidth="1"/>
-    <col min="5" max="5" width="35.08984375" customWidth="1"/>
+    <col min="2" max="2" width="11.53125" customWidth="1"/>
+    <col min="3" max="3" width="36.19921875" customWidth="1"/>
+    <col min="4" max="4" width="39.6640625" customWidth="1"/>
+    <col min="5" max="5" width="35.06640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A1" s="16" t="s">
         <v>9</v>
       </c>
@@ -4896,7 +5197,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="29.5" x14ac:dyDescent="0.75">
+    <row r="2" spans="1:5" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A2" s="6" t="s">
         <v>122</v>
       </c>
@@ -4913,7 +5214,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="29.5" x14ac:dyDescent="0.75">
+    <row r="3" spans="1:5" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A3" s="6" t="s">
         <v>141</v>
       </c>
@@ -4930,7 +5231,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A4" s="6" t="s">
         <v>106</v>
       </c>
@@ -4947,7 +5248,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A5" s="6" t="s">
         <v>151</v>
       </c>
@@ -4964,7 +5265,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="29.5" x14ac:dyDescent="0.75">
+    <row r="6" spans="1:5" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A6" s="6" t="s">
         <v>149</v>
       </c>
@@ -4981,7 +5282,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A7" s="29" t="s">
         <v>132</v>
       </c>
@@ -4998,7 +5299,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="29.5" x14ac:dyDescent="0.75">
+    <row r="8" spans="1:5" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A8" s="6" t="s">
         <v>145</v>
       </c>
@@ -5015,7 +5316,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="29.5" x14ac:dyDescent="0.75">
+    <row r="9" spans="1:5" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A9" s="6" t="s">
         <v>150</v>
       </c>
@@ -5043,15 +5344,15 @@
     <tabColor theme="6" tint="0.79998168889431442"/>
   </sheetPr>
   <dimension ref="A1:D8"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="21.54296875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="27.31640625" customWidth="1"/>
+    <col min="1" max="1" width="21.53125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="27.33203125" customWidth="1"/>
     <col min="3" max="3" width="28" style="5" customWidth="1"/>
-    <col min="4" max="4" width="71.453125" customWidth="1"/>
+    <col min="4" max="4" width="71.46484375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A1" s="2" t="s">
         <v>24</v>
       </c>
@@ -5065,7 +5366,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:4" ht="44.25" x14ac:dyDescent="0.75">
+    <row r="2" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A2" s="6" t="s">
         <v>100</v>
       </c>
@@ -5079,7 +5380,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A3" s="6" t="s">
         <v>157</v>
       </c>
@@ -5093,7 +5394,7 @@
         <v>155</v>
       </c>
     </row>
-    <row r="4" spans="1:4" ht="29.5" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:4" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A4" s="6" t="s">
         <v>156</v>
       </c>
@@ -5107,7 +5408,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A5" s="6" t="s">
         <v>123</v>
       </c>
@@ -5121,7 +5422,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A6" s="6" t="s">
         <v>247</v>
       </c>
@@ -5135,7 +5436,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A7" s="6" t="s">
         <v>468</v>
       </c>
@@ -5149,7 +5450,7 @@
         <v>470</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.75">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.45">
       <c r="A8" s="6" t="s">
         <v>485</v>
       </c>
@@ -5183,20 +5484,20 @@
   <sheetPr>
     <tabColor theme="7" tint="0.59999389629810485"/>
   </sheetPr>
-  <dimension ref="A1:H32"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <dimension ref="A1:H64"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="58.08984375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="58.06640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="71.86328125" customWidth="1"/>
     <col min="3" max="3" width="59.1328125" style="5" customWidth="1"/>
-    <col min="4" max="4" width="44.54296875" style="5" customWidth="1"/>
-    <col min="5" max="5" width="36.2265625" customWidth="1"/>
+    <col min="4" max="4" width="44.53125" style="5" customWidth="1"/>
+    <col min="5" max="5" width="36.19921875" customWidth="1"/>
     <col min="6" max="6" width="22" customWidth="1"/>
-    <col min="7" max="7" width="11.08984375" customWidth="1"/>
-    <col min="8" max="8" width="37.54296875" style="5" customWidth="1"/>
+    <col min="7" max="7" width="11.06640625" customWidth="1"/>
+    <col min="8" max="8" width="37.53125" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="14" customFormat="1" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:8" s="14" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
@@ -5222,7 +5523,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.75">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A2" s="7" t="str">
         <f>"http://hl7.eu/fhir/ig/oah/StructureDefinition/"&amp;LogicalModels!$A$7</f>
         <v>http://hl7.eu/fhir/ig/oah/StructureDefinition/HealthIndicators</v>
@@ -5247,7 +5548,7 @@
       </c>
       <c r="H2" s="8"/>
     </row>
-    <row r="3" spans="1:8" ht="29.5" x14ac:dyDescent="0.75">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A3" s="7" t="str">
         <f>"http://hl7.eu/fhir/ig/oah/StructureDefinition/"&amp;LogicalModels!$A$7</f>
         <v>http://hl7.eu/fhir/ig/oah/StructureDefinition/HealthIndicators</v>
@@ -5273,11 +5574,9 @@
       <c r="G3" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="H3" s="8" t="s">
-        <v>167</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.75">
+      <c r="H3" s="8"/>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A4" s="7" t="str">
         <f>"http://hl7.eu/fhir/ig/oah/StructureDefinition/"&amp;LogicalModels!$A$7</f>
         <v>http://hl7.eu/fhir/ig/oah/StructureDefinition/HealthIndicators</v>
@@ -5300,11 +5599,9 @@
       <c r="G4" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="H4" s="8" t="s">
-        <v>168</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.75">
+      <c r="H4" s="8"/>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A5" s="7" t="str">
         <f>"http://hl7.eu/fhir/ig/oah/StructureDefinition/"&amp;LogicalModels!$A$7</f>
         <v>http://hl7.eu/fhir/ig/oah/StructureDefinition/HealthIndicators</v>
@@ -5327,11 +5624,9 @@
       <c r="G5" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="H5" s="8" t="s">
-        <v>169</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" ht="44.25" x14ac:dyDescent="0.75">
+      <c r="H5" s="8"/>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A6" s="7" t="str">
         <f>"http://hl7.eu/fhir/ig/oah/StructureDefinition/"&amp;LogicalModels!$A$7</f>
         <v>http://hl7.eu/fhir/ig/oah/StructureDefinition/HealthIndicators</v>
@@ -5354,11 +5649,9 @@
       <c r="G6" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="H6" s="8" t="s">
-        <v>192</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" ht="44.25" x14ac:dyDescent="0.75">
+      <c r="H6" s="8"/>
+    </row>
+    <row r="7" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A7" s="7" t="str">
         <f>"http://hl7.eu/fhir/ig/oah/StructureDefinition/"&amp;LogicalModels!$A$7</f>
         <v>http://hl7.eu/fhir/ig/oah/StructureDefinition/HealthIndicators</v>
@@ -5381,11 +5674,9 @@
       <c r="G7" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="H7" s="8" t="s">
-        <v>193</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.75">
+      <c r="H7" s="8"/>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A8" s="7" t="str">
         <f>"http://hl7.eu/fhir/ig/oah/StructureDefinition/"&amp;LogicalModels!$A$7</f>
         <v>http://hl7.eu/fhir/ig/oah/StructureDefinition/HealthIndicators</v>
@@ -5408,11 +5699,9 @@
       <c r="G8" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="H8" s="8" t="s">
-        <v>170</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" ht="29.5" x14ac:dyDescent="0.75">
+      <c r="H8" s="8"/>
+    </row>
+    <row r="9" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A9" s="7" t="str">
         <f>"http://hl7.eu/fhir/ig/oah/StructureDefinition/"&amp;LogicalModels!$A$7</f>
         <v>http://hl7.eu/fhir/ig/oah/StructureDefinition/HealthIndicators</v>
@@ -5437,7 +5726,7 @@
       </c>
       <c r="H9" s="8"/>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.75">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A10" s="7" t="str">
         <f>"http://hl7.eu/fhir/ig/oah/StructureDefinition/"&amp;LogicalModels!$A$7</f>
         <v>http://hl7.eu/fhir/ig/oah/StructureDefinition/HealthIndicators</v>
@@ -5460,11 +5749,9 @@
       <c r="G10" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="H10" s="8" t="s">
-        <v>171</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.75">
+      <c r="H10" s="8"/>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A11" s="7" t="str">
         <f>"http://hl7.eu/fhir/ig/oah/StructureDefinition/"&amp;LogicalModels!$A$7</f>
         <v>http://hl7.eu/fhir/ig/oah/StructureDefinition/HealthIndicators</v>
@@ -5487,11 +5774,9 @@
       <c r="G11" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="H11" s="8" t="s">
-        <v>172</v>
-      </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.75">
+      <c r="H11" s="8"/>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A12" s="7" t="str">
         <f>"http://hl7.eu/fhir/ig/oah/StructureDefinition/"&amp;LogicalModels!$A$7</f>
         <v>http://hl7.eu/fhir/ig/oah/StructureDefinition/HealthIndicators</v>
@@ -5514,11 +5799,9 @@
       <c r="G12" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="H12" s="8" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.75">
+      <c r="H12" s="8"/>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A13" s="7" t="str">
         <f>"http://hl7.eu/fhir/ig/oah/StructureDefinition/"&amp;LogicalModels!$A$7</f>
         <v>http://hl7.eu/fhir/ig/oah/StructureDefinition/HealthIndicators</v>
@@ -5543,7 +5826,7 @@
       </c>
       <c r="H13" s="8"/>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.75">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A14" s="7" t="str">
         <f>"http://hl7.eu/fhir/ig/oah/StructureDefinition/"&amp;LogicalModels!$A$7</f>
         <v>http://hl7.eu/fhir/ig/oah/StructureDefinition/HealthIndicators</v>
@@ -5566,11 +5849,9 @@
       <c r="G14" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="H14" s="8" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.75">
+      <c r="H14" s="8"/>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A15" s="7" t="str">
         <f>"http://hl7.eu/fhir/ig/oah/StructureDefinition/"&amp;LogicalModels!$A$7</f>
         <v>http://hl7.eu/fhir/ig/oah/StructureDefinition/HealthIndicators</v>
@@ -5593,11 +5874,9 @@
       <c r="G15" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="H15" s="8" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.75">
+      <c r="H15" s="8"/>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A16" s="7" t="str">
         <f>"http://hl7.eu/fhir/ig/oah/StructureDefinition/"&amp;LogicalModels!$A$7</f>
         <v>http://hl7.eu/fhir/ig/oah/StructureDefinition/HealthIndicators</v>
@@ -5620,11 +5899,9 @@
       <c r="G16" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="H16" s="8" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="17" spans="1:8" ht="29.5" x14ac:dyDescent="0.75">
+      <c r="H16" s="8"/>
+    </row>
+    <row r="17" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A17" s="7" t="str">
         <f>"http://hl7.eu/fhir/ig/oah/StructureDefinition/"&amp;LogicalModels!$A$7</f>
         <v>http://hl7.eu/fhir/ig/oah/StructureDefinition/HealthIndicators</v>
@@ -5647,11 +5924,9 @@
       <c r="G17" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="H17" s="8" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.75">
+      <c r="H17" s="8"/>
+    </row>
+    <row r="18" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A18" s="7" t="str">
         <f>"http://hl7.eu/fhir/ig/oah/StructureDefinition/"&amp;LogicalModels!$A$7</f>
         <v>http://hl7.eu/fhir/ig/oah/StructureDefinition/HealthIndicators</v>
@@ -5674,11 +5949,9 @@
       <c r="G18" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="H18" s="8" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.75">
+      <c r="H18" s="8"/>
+    </row>
+    <row r="19" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A19" s="7" t="str">
         <f>"http://hl7.eu/fhir/ig/oah/StructureDefinition/"&amp;LogicalModels!$A$7</f>
         <v>http://hl7.eu/fhir/ig/oah/StructureDefinition/HealthIndicators</v>
@@ -5701,11 +5974,9 @@
       <c r="G19" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="H19" s="8" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.75">
+      <c r="H19" s="8"/>
+    </row>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A20" s="7" t="str">
         <f>"http://hl7.eu/fhir/ig/oah/StructureDefinition/"&amp;LogicalModels!$A$7</f>
         <v>http://hl7.eu/fhir/ig/oah/StructureDefinition/HealthIndicators</v>
@@ -5728,11 +5999,9 @@
       <c r="G20" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="H20" s="8" t="s">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" ht="29.5" x14ac:dyDescent="0.75">
+      <c r="H20" s="8"/>
+    </row>
+    <row r="21" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A21" s="7" t="str">
         <f>"http://hl7.eu/fhir/ig/oah/StructureDefinition/"&amp;LogicalModels!$A$7</f>
         <v>http://hl7.eu/fhir/ig/oah/StructureDefinition/HealthIndicators</v>
@@ -5755,11 +6024,9 @@
       <c r="G21" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="H21" s="8" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.75">
+      <c r="H21" s="8"/>
+    </row>
+    <row r="22" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A22" s="7" t="str">
         <f>"http://hl7.eu/fhir/ig/oah/StructureDefinition/"&amp;LogicalModels!$A$7</f>
         <v>http://hl7.eu/fhir/ig/oah/StructureDefinition/HealthIndicators</v>
@@ -5782,11 +6049,9 @@
       <c r="G22" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="H22" s="8" t="s">
-        <v>182</v>
-      </c>
-    </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.75">
+      <c r="H22" s="8"/>
+    </row>
+    <row r="23" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A23" s="7" t="str">
         <f>"http://hl7.eu/fhir/ig/oah/StructureDefinition/"&amp;LogicalModels!$A$7</f>
         <v>http://hl7.eu/fhir/ig/oah/StructureDefinition/HealthIndicators</v>
@@ -5809,11 +6074,9 @@
       <c r="G23" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="H23" s="8" t="s">
-        <v>183</v>
-      </c>
-    </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.75">
+      <c r="H23" s="8"/>
+    </row>
+    <row r="24" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A24" s="7" t="str">
         <f>"http://hl7.eu/fhir/ig/oah/StructureDefinition/"&amp;LogicalModels!$A$7</f>
         <v>http://hl7.eu/fhir/ig/oah/StructureDefinition/HealthIndicators</v>
@@ -5838,7 +6101,7 @@
       </c>
       <c r="H24" s="8"/>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.75">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A25" s="7" t="str">
         <f>"http://hl7.eu/fhir/ig/oah/StructureDefinition/"&amp;LogicalModels!$A$7</f>
         <v>http://hl7.eu/fhir/ig/oah/StructureDefinition/HealthIndicators</v>
@@ -5861,11 +6124,9 @@
       <c r="G25" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="H25" s="8" t="s">
-        <v>184</v>
-      </c>
-    </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.75">
+      <c r="H25" s="8"/>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A26" s="7" t="str">
         <f>"http://hl7.eu/fhir/ig/oah/StructureDefinition/"&amp;LogicalModels!$A$7</f>
         <v>http://hl7.eu/fhir/ig/oah/StructureDefinition/HealthIndicators</v>
@@ -5888,11 +6149,9 @@
       <c r="G26" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="H26" s="8" t="s">
-        <v>185</v>
-      </c>
-    </row>
-    <row r="27" spans="1:8" ht="29.5" x14ac:dyDescent="0.75">
+      <c r="H26" s="8"/>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A27" s="7" t="str">
         <f>"http://hl7.eu/fhir/ig/oah/StructureDefinition/"&amp;LogicalModels!$A$7</f>
         <v>http://hl7.eu/fhir/ig/oah/StructureDefinition/HealthIndicators</v>
@@ -5915,11 +6174,9 @@
       <c r="G27" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="H27" s="8" t="s">
-        <v>186</v>
-      </c>
-    </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.75">
+      <c r="H27" s="8"/>
+    </row>
+    <row r="28" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A28" s="7" t="str">
         <f>"http://hl7.eu/fhir/ig/oah/StructureDefinition/"&amp;LogicalModels!$A$7</f>
         <v>http://hl7.eu/fhir/ig/oah/StructureDefinition/HealthIndicators</v>
@@ -5942,11 +6199,9 @@
       <c r="G28" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="H28" s="8" t="s">
-        <v>187</v>
-      </c>
-    </row>
-    <row r="29" spans="1:8" ht="29.5" x14ac:dyDescent="0.75">
+      <c r="H28" s="8"/>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A29" s="7" t="str">
         <f>"http://hl7.eu/fhir/ig/oah/StructureDefinition/"&amp;LogicalModels!$A$7</f>
         <v>http://hl7.eu/fhir/ig/oah/StructureDefinition/HealthIndicators</v>
@@ -5969,11 +6224,9 @@
       <c r="G29" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="H29" s="8" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.75">
+      <c r="H29" s="8"/>
+    </row>
+    <row r="30" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A30" s="7" t="str">
         <f>"http://hl7.eu/fhir/ig/oah/StructureDefinition/"&amp;LogicalModels!$A$7</f>
         <v>http://hl7.eu/fhir/ig/oah/StructureDefinition/HealthIndicators</v>
@@ -5996,11 +6249,9 @@
       <c r="G30" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="H30" s="8" t="s">
-        <v>189</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.75">
+      <c r="H30" s="8"/>
+    </row>
+    <row r="31" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A31" s="7" t="str">
         <f>"http://hl7.eu/fhir/ig/oah/StructureDefinition/"&amp;LogicalModels!$A$7</f>
         <v>http://hl7.eu/fhir/ig/oah/StructureDefinition/HealthIndicators</v>
@@ -6023,11 +6274,9 @@
       <c r="G31" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="H31" s="8" t="s">
-        <v>190</v>
-      </c>
-    </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.75">
+      <c r="H31" s="8"/>
+    </row>
+    <row r="32" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A32" s="7" t="str">
         <f>"http://hl7.eu/fhir/ig/oah/StructureDefinition/"&amp;LogicalModels!$A$7</f>
         <v>http://hl7.eu/fhir/ig/oah/StructureDefinition/HealthIndicators</v>
@@ -6043,25 +6292,856 @@
         <f>HealthIndicatorsOah!D32</f>
         <v>% of people with Yersinia enterocolitica</v>
       </c>
-      <c r="E32" s="27" t="s">
+      <c r="E32" s="8" t="s">
         <v>27</v>
       </c>
       <c r="F32" s="6"/>
       <c r="G32" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="H32" s="8" t="s">
-        <v>190</v>
-      </c>
+      <c r="H32" s="8"/>
+    </row>
+    <row r="33" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A33" s="7" t="str">
+        <f>"http://hl7.eu/fhir/ig/oah/StructureDefinition/"&amp;LogicalModels!$A$7</f>
+        <v>http://hl7.eu/fhir/ig/oah/StructureDefinition/HealthIndicators</v>
+      </c>
+      <c r="B33" s="40" t="s">
+        <v>491</v>
+      </c>
+      <c r="C33" s="8" t="str">
+        <f>HealthIndicatorsOah!A33</f>
+        <v>causesOfDeath</v>
+      </c>
+      <c r="D33" s="8" t="str">
+        <f>HealthIndicatorsOah!D33</f>
+        <v>Cases of death</v>
+      </c>
+      <c r="E33" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="F33" s="6"/>
+      <c r="G33" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="H33" s="8"/>
+    </row>
+    <row r="34" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A34" s="7" t="str">
+        <f>"http://hl7.eu/fhir/ig/oah/StructureDefinition/"&amp;LogicalModels!$A$7</f>
+        <v>http://hl7.eu/fhir/ig/oah/StructureDefinition/HealthIndicators</v>
+      </c>
+      <c r="B34" s="40" t="s">
+        <v>491</v>
+      </c>
+      <c r="C34" s="8" t="str">
+        <f>HealthIndicatorsOah!A34</f>
+        <v>causesOfDeath.tbc</v>
+      </c>
+      <c r="D34" s="8" t="str">
+        <f>HealthIndicatorsOah!D34</f>
+        <v>% of deaths due to TBC</v>
+      </c>
+      <c r="E34" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="F34" s="6"/>
+      <c r="G34" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="H34" s="8"/>
+    </row>
+    <row r="35" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A35" s="7" t="str">
+        <f>"http://hl7.eu/fhir/ig/oah/StructureDefinition/"&amp;LogicalModels!$A$7</f>
+        <v>http://hl7.eu/fhir/ig/oah/StructureDefinition/HealthIndicators</v>
+      </c>
+      <c r="B35" s="40" t="s">
+        <v>491</v>
+      </c>
+      <c r="C35" s="8" t="str">
+        <f>HealthIndicatorsOah!A35</f>
+        <v>causesOfDeath.viralHepatitis</v>
+      </c>
+      <c r="D35" s="8" t="str">
+        <f>HealthIndicatorsOah!D35</f>
+        <v>% of deaths due to Viral Hepatitis</v>
+      </c>
+      <c r="E35" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="F35" s="6"/>
+      <c r="G35" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="H35" s="8"/>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A36" s="7" t="str">
+        <f>"http://hl7.eu/fhir/ig/oah/StructureDefinition/"&amp;LogicalModels!$A$7</f>
+        <v>http://hl7.eu/fhir/ig/oah/StructureDefinition/HealthIndicators</v>
+      </c>
+      <c r="B36" s="40" t="s">
+        <v>491</v>
+      </c>
+      <c r="C36" s="8" t="str">
+        <f>HealthIndicatorsOah!A36</f>
+        <v>causesOfDeath.infectiveAndParasitic</v>
+      </c>
+      <c r="D36" s="8" t="str">
+        <f>HealthIndicatorsOah!D36</f>
+        <v>% of deaths due to infective and parasitic diseases</v>
+      </c>
+      <c r="E36" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="F36" s="6"/>
+      <c r="G36" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="H36" s="8"/>
+    </row>
+    <row r="37" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A37" s="7" t="str">
+        <f>"http://hl7.eu/fhir/ig/oah/StructureDefinition/"&amp;LogicalModels!$A$7</f>
+        <v>http://hl7.eu/fhir/ig/oah/StructureDefinition/HealthIndicators</v>
+      </c>
+      <c r="B37" s="40" t="s">
+        <v>491</v>
+      </c>
+      <c r="C37" s="8" t="str">
+        <f>HealthIndicatorsOah!A37</f>
+        <v>causesOfDeath.bloodAndHematopoieticOrgans</v>
+      </c>
+      <c r="D37" s="8" t="str">
+        <f>HealthIndicatorsOah!D37</f>
+        <v>% of deaths due to diseases of the blood and hematopoietic organs</v>
+      </c>
+      <c r="E37" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="F37" s="6"/>
+      <c r="G37" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="H37" s="8"/>
+    </row>
+    <row r="38" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A38" s="7" t="str">
+        <f>"http://hl7.eu/fhir/ig/oah/StructureDefinition/"&amp;LogicalModels!$A$7</f>
+        <v>http://hl7.eu/fhir/ig/oah/StructureDefinition/HealthIndicators</v>
+      </c>
+      <c r="B38" s="40" t="s">
+        <v>491</v>
+      </c>
+      <c r="C38" s="8" t="str">
+        <f>HealthIndicatorsOah!A38</f>
+        <v>causesOfDeath.diabetesMellitus</v>
+      </c>
+      <c r="D38" s="8" t="str">
+        <f>HealthIndicatorsOah!D38</f>
+        <v>% of deaths due to Diabetes Mellitus</v>
+      </c>
+      <c r="E38" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="F38" s="6"/>
+      <c r="G38" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="H38" s="8"/>
+    </row>
+    <row r="39" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A39" s="7" t="str">
+        <f>"http://hl7.eu/fhir/ig/oah/StructureDefinition/"&amp;LogicalModels!$A$7</f>
+        <v>http://hl7.eu/fhir/ig/oah/StructureDefinition/HealthIndicators</v>
+      </c>
+      <c r="B39" s="40" t="s">
+        <v>491</v>
+      </c>
+      <c r="C39" s="8" t="str">
+        <f>HealthIndicatorsOah!A39</f>
+        <v>causesOfDeath.endocrineNutritionalMetabolic</v>
+      </c>
+      <c r="D39" s="8" t="str">
+        <f>HealthIndicatorsOah!D39</f>
+        <v>% of deaths due to endocrine, nutritional and metabolic diseases</v>
+      </c>
+      <c r="E39" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="F39" s="6"/>
+      <c r="G39" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="H39" s="8"/>
+    </row>
+    <row r="40" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A40" s="7" t="str">
+        <f>"http://hl7.eu/fhir/ig/oah/StructureDefinition/"&amp;LogicalModels!$A$7</f>
+        <v>http://hl7.eu/fhir/ig/oah/StructureDefinition/HealthIndicators</v>
+      </c>
+      <c r="B40" s="40" t="s">
+        <v>491</v>
+      </c>
+      <c r="C40" s="8" t="str">
+        <f>HealthIndicatorsOah!A40</f>
+        <v>causesOfDeath.ischemicHeart</v>
+      </c>
+      <c r="D40" s="8" t="str">
+        <f>HealthIndicatorsOah!D40</f>
+        <v>% of deaths due to ischemic diseases of the heart</v>
+      </c>
+      <c r="E40" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="F40" s="6"/>
+      <c r="G40" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="H40" s="8"/>
+    </row>
+    <row r="41" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A41" s="7" t="str">
+        <f>"http://hl7.eu/fhir/ig/oah/StructureDefinition/"&amp;LogicalModels!$A$7</f>
+        <v>http://hl7.eu/fhir/ig/oah/StructureDefinition/HealthIndicators</v>
+      </c>
+      <c r="B41" s="40" t="s">
+        <v>491</v>
+      </c>
+      <c r="C41" s="8" t="str">
+        <f>HealthIndicatorsOah!A41</f>
+        <v>causesOfDeath.otherHeart</v>
+      </c>
+      <c r="D41" s="8" t="str">
+        <f>HealthIndicatorsOah!D41</f>
+        <v>% of deaths due to other diseases of the heart</v>
+      </c>
+      <c r="E41" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="F41" s="6"/>
+      <c r="G41" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="H41" s="8"/>
+    </row>
+    <row r="42" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A42" s="7" t="str">
+        <f>"http://hl7.eu/fhir/ig/oah/StructureDefinition/"&amp;LogicalModels!$A$7</f>
+        <v>http://hl7.eu/fhir/ig/oah/StructureDefinition/HealthIndicators</v>
+      </c>
+      <c r="B42" s="40" t="s">
+        <v>491</v>
+      </c>
+      <c r="C42" s="8" t="str">
+        <f>HealthIndicatorsOah!A42</f>
+        <v xml:space="preserve">causesOfDeath.otherCirculatorySystem </v>
+      </c>
+      <c r="D42" s="8" t="str">
+        <f>HealthIndicatorsOah!D42</f>
+        <v xml:space="preserve">% of deaths due to other diseases of the circulatory system </v>
+      </c>
+      <c r="E42" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="F42" s="6"/>
+      <c r="G42" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="H42" s="8"/>
+    </row>
+    <row r="43" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A43" s="7" t="str">
+        <f>"http://hl7.eu/fhir/ig/oah/StructureDefinition/"&amp;LogicalModels!$A$7</f>
+        <v>http://hl7.eu/fhir/ig/oah/StructureDefinition/HealthIndicators</v>
+      </c>
+      <c r="B43" s="40" t="s">
+        <v>491</v>
+      </c>
+      <c r="C43" s="8" t="str">
+        <f>HealthIndicatorsOah!A43</f>
+        <v>causesOfDeath.pneumonia</v>
+      </c>
+      <c r="D43" s="8" t="str">
+        <f>HealthIndicatorsOah!D43</f>
+        <v>% of deaths due to Pneumonia</v>
+      </c>
+      <c r="E43" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="F43" s="6"/>
+      <c r="G43" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="H43" s="8"/>
+    </row>
+    <row r="44" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A44" s="7" t="str">
+        <f>"http://hl7.eu/fhir/ig/oah/StructureDefinition/"&amp;LogicalModels!$A$7</f>
+        <v>http://hl7.eu/fhir/ig/oah/StructureDefinition/HealthIndicators</v>
+      </c>
+      <c r="B44" s="40" t="s">
+        <v>491</v>
+      </c>
+      <c r="C44" s="8" t="str">
+        <f>HealthIndicatorsOah!A44</f>
+        <v>causesOfDeath.chronicLowerRespiratory</v>
+      </c>
+      <c r="D44" s="8" t="str">
+        <f>HealthIndicatorsOah!D44</f>
+        <v>% of deaths due to chronic diseases of the lower respiratory tract</v>
+      </c>
+      <c r="E44" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="F44" s="6"/>
+      <c r="G44" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="H44" s="8"/>
+    </row>
+    <row r="45" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A45" s="7" t="str">
+        <f>"http://hl7.eu/fhir/ig/oah/StructureDefinition/"&amp;LogicalModels!$A$7</f>
+        <v>http://hl7.eu/fhir/ig/oah/StructureDefinition/HealthIndicators</v>
+      </c>
+      <c r="B45" s="40" t="s">
+        <v>491</v>
+      </c>
+      <c r="C45" s="8" t="str">
+        <f>HealthIndicatorsOah!A45</f>
+        <v>causesOfDeath.otherRespiratorySystem</v>
+      </c>
+      <c r="D45" s="8" t="str">
+        <f>HealthIndicatorsOah!D45</f>
+        <v>% of deaths due to other diseases of the respiratory system</v>
+      </c>
+      <c r="E45" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="F45" s="6"/>
+      <c r="G45" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="H45" s="8"/>
+    </row>
+    <row r="46" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A46" s="7" t="str">
+        <f>"http://hl7.eu/fhir/ig/oah/StructureDefinition/"&amp;LogicalModels!$A$7</f>
+        <v>http://hl7.eu/fhir/ig/oah/StructureDefinition/HealthIndicators</v>
+      </c>
+      <c r="B46" s="40" t="s">
+        <v>491</v>
+      </c>
+      <c r="C46" s="8" t="str">
+        <f>HealthIndicatorsOah!A46</f>
+        <v>causesOfDeath.SkinSubcutaneousTissue</v>
+      </c>
+      <c r="D46" s="8" t="str">
+        <f>HealthIndicatorsOah!D46</f>
+        <v>% of deaths due to diseases of the skin and subcutaneous tissue</v>
+      </c>
+      <c r="E46" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="F46" s="6"/>
+      <c r="G46" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="H46" s="8"/>
+    </row>
+    <row r="47" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A47" s="7" t="str">
+        <f>"http://hl7.eu/fhir/ig/oah/StructureDefinition/"&amp;LogicalModels!$A$7</f>
+        <v>http://hl7.eu/fhir/ig/oah/StructureDefinition/HealthIndicators</v>
+      </c>
+      <c r="B47" s="40" t="s">
+        <v>491</v>
+      </c>
+      <c r="C47" s="8" t="str">
+        <f>HealthIndicatorsOah!A47</f>
+        <v>causesOfDeath.accidentalPoisoning</v>
+      </c>
+      <c r="D47" s="8" t="str">
+        <f>HealthIndicatorsOah!D47</f>
+        <v>% of deaths due to accidental poisoning</v>
+      </c>
+      <c r="E47" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="F47" s="6"/>
+      <c r="G47" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="H47" s="8"/>
+    </row>
+    <row r="48" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A48" s="7" t="str">
+        <f>"http://hl7.eu/fhir/ig/oah/StructureDefinition/"&amp;LogicalModels!$A$7</f>
+        <v>http://hl7.eu/fhir/ig/oah/StructureDefinition/HealthIndicators</v>
+      </c>
+      <c r="B48" s="40" t="s">
+        <v>491</v>
+      </c>
+      <c r="C48" s="8" t="str">
+        <f>HealthIndicatorsOah!A48</f>
+        <v>causesOfDeath.malignantTumor</v>
+      </c>
+      <c r="D48" s="8" t="str">
+        <f>HealthIndicatorsOah!D48</f>
+        <v>% of deaths due to Malignant Tumors</v>
+      </c>
+      <c r="E48" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="F48" s="6"/>
+      <c r="G48" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="H48" s="8"/>
+    </row>
+    <row r="49" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A49" s="7" t="str">
+        <f>"http://hl7.eu/fhir/ig/oah/StructureDefinition/"&amp;LogicalModels!$A$7</f>
+        <v>http://hl7.eu/fhir/ig/oah/StructureDefinition/HealthIndicators</v>
+      </c>
+      <c r="B49" s="40" t="s">
+        <v>491</v>
+      </c>
+      <c r="C49" s="8" t="str">
+        <f>HealthIndicatorsOah!A49</f>
+        <v xml:space="preserve">causesOfDeath.healthcareSensitiveCauses </v>
+      </c>
+      <c r="D49" s="8" t="str">
+        <f>HealthIndicatorsOah!D49</f>
+        <v xml:space="preserve">% of deaths due to Healthcare-Sensitive Causes </v>
+      </c>
+      <c r="E49" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="F49" s="6"/>
+      <c r="G49" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="H49" s="8"/>
+    </row>
+    <row r="50" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A50" s="7" t="str">
+        <f>"http://hl7.eu/fhir/ig/oah/StructureDefinition/"&amp;LogicalModels!$A$7</f>
+        <v>http://hl7.eu/fhir/ig/oah/StructureDefinition/HealthIndicators</v>
+      </c>
+      <c r="B50" s="40" t="s">
+        <v>491</v>
+      </c>
+      <c r="C50" s="8" t="str">
+        <f>HealthIndicatorsOah!A50</f>
+        <v>causesOfDeath.winterExcess</v>
+      </c>
+      <c r="D50" s="8" t="str">
+        <f>HealthIndicatorsOah!D50</f>
+        <v>% of Excess Mortality in Winter</v>
+      </c>
+      <c r="E50" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="F50" s="6"/>
+      <c r="G50" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="H50" s="8"/>
+    </row>
+    <row r="51" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A51" s="7" t="str">
+        <f>"http://hl7.eu/fhir/ig/oah/StructureDefinition/"&amp;LogicalModels!$A$7</f>
+        <v>http://hl7.eu/fhir/ig/oah/StructureDefinition/HealthIndicators</v>
+      </c>
+      <c r="B51" s="40" t="s">
+        <v>491</v>
+      </c>
+      <c r="C51" s="8" t="str">
+        <f>HealthIndicatorsOah!A51</f>
+        <v>causesOfDeath.all</v>
+      </c>
+      <c r="D51" s="8" t="str">
+        <f>HealthIndicatorsOah!D51</f>
+        <v>% of deaths due to all causes</v>
+      </c>
+      <c r="E51" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="F51" s="6"/>
+      <c r="G51" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="H51" s="8"/>
+    </row>
+    <row r="52" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A52" s="7" t="str">
+        <f>"http://hl7.eu/fhir/ig/oah/StructureDefinition/"&amp;LogicalModels!$A$7</f>
+        <v>http://hl7.eu/fhir/ig/oah/StructureDefinition/HealthIndicators</v>
+      </c>
+      <c r="B52" s="40" t="s">
+        <v>491</v>
+      </c>
+      <c r="C52" s="8" t="str">
+        <f>HealthIndicatorsOah!A52</f>
+        <v>causesOfDeath.cancer</v>
+      </c>
+      <c r="D52" s="8" t="str">
+        <f>HealthIndicatorsOah!D52</f>
+        <v>% of deaths due to cancer</v>
+      </c>
+      <c r="E52" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="F52" s="6"/>
+      <c r="G52" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="H52" s="8"/>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A53" s="7" t="str">
+        <f>"http://hl7.eu/fhir/ig/oah/StructureDefinition/"&amp;LogicalModels!$A$7</f>
+        <v>http://hl7.eu/fhir/ig/oah/StructureDefinition/HealthIndicators</v>
+      </c>
+      <c r="B53" s="40" t="s">
+        <v>491</v>
+      </c>
+      <c r="C53" s="8" t="str">
+        <f>HealthIndicatorsOah!A53</f>
+        <v>causesOfDeath.diabetes</v>
+      </c>
+      <c r="D53" s="8" t="str">
+        <f>HealthIndicatorsOah!D53</f>
+        <v>% of deaths due to diabetes</v>
+      </c>
+      <c r="E53" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="F53" s="6"/>
+      <c r="G53" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="H53" s="8"/>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A54" s="7" t="str">
+        <f>"http://hl7.eu/fhir/ig/oah/StructureDefinition/"&amp;LogicalModels!$A$7</f>
+        <v>http://hl7.eu/fhir/ig/oah/StructureDefinition/HealthIndicators</v>
+      </c>
+      <c r="B54" s="40" t="s">
+        <v>491</v>
+      </c>
+      <c r="C54" s="8" t="str">
+        <f>HealthIndicatorsOah!A54</f>
+        <v>causesOfDeath.cardiovascular</v>
+      </c>
+      <c r="D54" s="8" t="str">
+        <f>HealthIndicatorsOah!D54</f>
+        <v>% of deaths due to cardiovascular disease</v>
+      </c>
+      <c r="E54" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="F54" s="6"/>
+      <c r="G54" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="H54" s="8"/>
+    </row>
+    <row r="55" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A55" s="7" t="str">
+        <f>"http://hl7.eu/fhir/ig/oah/StructureDefinition/"&amp;LogicalModels!$A$7</f>
+        <v>http://hl7.eu/fhir/ig/oah/StructureDefinition/HealthIndicators</v>
+      </c>
+      <c r="B55" s="40" t="s">
+        <v>491</v>
+      </c>
+      <c r="C55" s="8" t="str">
+        <f>HealthIndicatorsOah!A55</f>
+        <v>causesOfDeath.respiratory</v>
+      </c>
+      <c r="D55" s="8" t="str">
+        <f>HealthIndicatorsOah!D55</f>
+        <v>% of deaths due to respiratory disease</v>
+      </c>
+      <c r="E55" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="F55" s="6"/>
+      <c r="G55" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="H55" s="8"/>
+    </row>
+    <row r="56" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A56" s="7" t="str">
+        <f>"http://hl7.eu/fhir/ig/oah/StructureDefinition/"&amp;LogicalModels!$A$7</f>
+        <v>http://hl7.eu/fhir/ig/oah/StructureDefinition/HealthIndicators</v>
+      </c>
+      <c r="B56" s="40" t="s">
+        <v>491</v>
+      </c>
+      <c r="C56" s="8" t="str">
+        <f>HealthIndicatorsOah!A56</f>
+        <v>causesOfDeath.COPDLungCancer</v>
+      </c>
+      <c r="D56" s="8" t="str">
+        <f>HealthIndicatorsOah!D56</f>
+        <v>% of deaths due to COPD and lung cancer</v>
+      </c>
+      <c r="E56" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="F56" s="6"/>
+      <c r="G56" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="H56" s="8"/>
+    </row>
+    <row r="57" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A57" s="7" t="str">
+        <f>"http://hl7.eu/fhir/ig/oah/StructureDefinition/"&amp;LogicalModels!$A$7</f>
+        <v>http://hl7.eu/fhir/ig/oah/StructureDefinition/HealthIndicators</v>
+      </c>
+      <c r="B57" s="40" t="s">
+        <v>491</v>
+      </c>
+      <c r="C57" s="8" t="str">
+        <f>HealthIndicatorsOah!A57</f>
+        <v>hospitalization</v>
+      </c>
+      <c r="D57" s="8">
+        <f>HealthIndicatorsOah!D57</f>
+        <v>0</v>
+      </c>
+      <c r="E57" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="F57" s="6"/>
+      <c r="G57" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="H57" s="8"/>
+    </row>
+    <row r="58" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A58" s="7" t="str">
+        <f>"http://hl7.eu/fhir/ig/oah/StructureDefinition/"&amp;LogicalModels!$A$7</f>
+        <v>http://hl7.eu/fhir/ig/oah/StructureDefinition/HealthIndicators</v>
+      </c>
+      <c r="B58" s="40" t="s">
+        <v>491</v>
+      </c>
+      <c r="C58" s="8" t="str">
+        <f>HealthIndicatorsOah!A58</f>
+        <v>hospitalization.diabetesMellitus</v>
+      </c>
+      <c r="D58" s="8" t="str">
+        <f>HealthIndicatorsOah!D58</f>
+        <v>% of hospitalizations due to Diabetes Mellitus</v>
+      </c>
+      <c r="E58" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="F58" s="6"/>
+      <c r="G58" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="H58" s="8"/>
+    </row>
+    <row r="59" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A59" s="7" t="str">
+        <f>"http://hl7.eu/fhir/ig/oah/StructureDefinition/"&amp;LogicalModels!$A$7</f>
+        <v>http://hl7.eu/fhir/ig/oah/StructureDefinition/HealthIndicators</v>
+      </c>
+      <c r="B59" s="40" t="s">
+        <v>491</v>
+      </c>
+      <c r="C59" s="8" t="str">
+        <f>HealthIndicatorsOah!A59</f>
+        <v>hospitalization.malignantTumor</v>
+      </c>
+      <c r="D59" s="8" t="str">
+        <f>HealthIndicatorsOah!D59</f>
+        <v>% of hospitalizations due to malignant tumors</v>
+      </c>
+      <c r="E59" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="F59" s="6"/>
+      <c r="G59" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="H59" s="8"/>
+    </row>
+    <row r="60" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A60" s="7" t="str">
+        <f>"http://hl7.eu/fhir/ig/oah/StructureDefinition/"&amp;LogicalModels!$A$7</f>
+        <v>http://hl7.eu/fhir/ig/oah/StructureDefinition/HealthIndicators</v>
+      </c>
+      <c r="B60" s="40" t="s">
+        <v>491</v>
+      </c>
+      <c r="C60" s="8" t="str">
+        <f>HealthIndicatorsOah!A60</f>
+        <v>hospitalization.hypertension</v>
+      </c>
+      <c r="D60" s="8" t="str">
+        <f>HealthIndicatorsOah!D60</f>
+        <v>% of hospitalizations due to Hypertension</v>
+      </c>
+      <c r="E60" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="F60" s="6"/>
+      <c r="G60" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="H60" s="8"/>
+    </row>
+    <row r="61" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A61" s="7" t="str">
+        <f>"http://hl7.eu/fhir/ig/oah/StructureDefinition/"&amp;LogicalModels!$A$7</f>
+        <v>http://hl7.eu/fhir/ig/oah/StructureDefinition/HealthIndicators</v>
+      </c>
+      <c r="B61" s="40" t="s">
+        <v>491</v>
+      </c>
+      <c r="C61" s="8" t="str">
+        <f>HealthIndicatorsOah!A61</f>
+        <v>hospitalization.cardiovascular</v>
+      </c>
+      <c r="D61" s="8" t="str">
+        <f>HealthIndicatorsOah!D61</f>
+        <v>% of hospitalizations due to Circulatory System Diseases</v>
+      </c>
+      <c r="E61" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="F61" s="6"/>
+      <c r="G61" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="H61" s="8"/>
+    </row>
+    <row r="62" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A62" s="7" t="str">
+        <f>"http://hl7.eu/fhir/ig/oah/StructureDefinition/"&amp;LogicalModels!$A$7</f>
+        <v>http://hl7.eu/fhir/ig/oah/StructureDefinition/HealthIndicators</v>
+      </c>
+      <c r="B62" s="40" t="s">
+        <v>491</v>
+      </c>
+      <c r="C62" s="8" t="str">
+        <f>HealthIndicatorsOah!A62</f>
+        <v>hospitalization.respiratory</v>
+      </c>
+      <c r="D62" s="8" t="str">
+        <f>HealthIndicatorsOah!D62</f>
+        <v>% of hospitalizations due to respiratory diseases</v>
+      </c>
+      <c r="E62" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="F62" s="6"/>
+      <c r="G62" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="H62" s="8"/>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.45">
+      <c r="A63" s="7" t="str">
+        <f>"http://hl7.eu/fhir/ig/oah/StructureDefinition/"&amp;LogicalModels!$A$7</f>
+        <v>http://hl7.eu/fhir/ig/oah/StructureDefinition/HealthIndicators</v>
+      </c>
+      <c r="B63" s="40" t="s">
+        <v>491</v>
+      </c>
+      <c r="C63" s="8" t="str">
+        <f>HealthIndicatorsOah!A63</f>
+        <v>hospitalization.asthma</v>
+      </c>
+      <c r="D63" s="8" t="str">
+        <f>HealthIndicatorsOah!D63</f>
+        <v>% of hospitalizations for Asthma</v>
+      </c>
+      <c r="E63" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="F63" s="6"/>
+      <c r="G63" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="H63" s="8"/>
+    </row>
+    <row r="64" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
+      <c r="A64" s="7" t="str">
+        <f>"http://hl7.eu/fhir/ig/oah/StructureDefinition/"&amp;LogicalModels!$A$7</f>
+        <v>http://hl7.eu/fhir/ig/oah/StructureDefinition/HealthIndicators</v>
+      </c>
+      <c r="B64" s="40" t="s">
+        <v>491</v>
+      </c>
+      <c r="C64" s="8" t="str">
+        <f>HealthIndicatorsOah!A64</f>
+        <v>hospitalization.avoidablePrimaryPrevention</v>
+      </c>
+      <c r="D64" s="8" t="str">
+        <f>HealthIndicatorsOah!D64</f>
+        <v xml:space="preserve">% of hospitalizations avoidable by primary prevention
+</v>
+      </c>
+      <c r="E64" s="8" t="s">
+        <v>27</v>
+      </c>
+      <c r="F64" s="6"/>
+      <c r="G64" s="6" t="s">
+        <v>7</v>
+      </c>
+      <c r="H64" s="8"/>
     </row>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="A1" r:id="rId1" display="http://hl7.eu/fhir/hdr/StructureDefinition/composition-eu-hdr" xr:uid="{7ECBB079-59D4-430D-A63D-DA6562D0849D}"/>
     <hyperlink ref="B2" r:id="rId2" xr:uid="{90723054-B35E-4066-95F6-D6C3AEAB7AC6}"/>
     <hyperlink ref="B3:B32" r:id="rId3" display="http://hl7.eu/fhir/ig/oah/StructureDefinition/observation-health-measure-oah" xr:uid="{71C462B5-7360-4020-99CD-1D62E47FDF48}"/>
+    <hyperlink ref="B33" r:id="rId4" xr:uid="{A0C2A0F4-FF28-4D4B-932C-2CB02832C153}"/>
+    <hyperlink ref="B34" r:id="rId5" xr:uid="{A8EBED29-ADA1-4E0F-AC36-77C079531A7D}"/>
+    <hyperlink ref="B35" r:id="rId6" xr:uid="{A4C037E0-5996-4F31-BDA8-EBCF245E1784}"/>
+    <hyperlink ref="B36" r:id="rId7" xr:uid="{F6AB5A71-196D-4074-889F-86CE62AB2D53}"/>
+    <hyperlink ref="B37" r:id="rId8" xr:uid="{6992DCD7-A3DA-418C-B173-0358C61AFA95}"/>
+    <hyperlink ref="B38" r:id="rId9" xr:uid="{CFE2FB17-A4F0-4BD6-B858-9567CDE2819A}"/>
+    <hyperlink ref="B39" r:id="rId10" xr:uid="{393A5CD2-A97F-47D5-9DA4-A7F7271D0645}"/>
+    <hyperlink ref="B40" r:id="rId11" xr:uid="{9D507041-BF92-4851-B697-BB9B8062193E}"/>
+    <hyperlink ref="B41" r:id="rId12" xr:uid="{12178CA8-8BF0-4551-86A1-0A56956A1FE2}"/>
+    <hyperlink ref="B42" r:id="rId13" xr:uid="{B98F0FD6-3803-424A-826B-C997D95CB0C3}"/>
+    <hyperlink ref="B43" r:id="rId14" xr:uid="{E6A13994-A7D7-4782-A8DB-73D8A2B3290E}"/>
+    <hyperlink ref="B44" r:id="rId15" xr:uid="{7FC4C96E-74B1-4B1F-930E-4E312AD2E826}"/>
+    <hyperlink ref="B45" r:id="rId16" xr:uid="{46A807D9-9027-40AE-93B9-C6B209AF58DA}"/>
+    <hyperlink ref="B46" r:id="rId17" xr:uid="{68C94EB1-7235-499D-8F21-11C69832E0F3}"/>
+    <hyperlink ref="B47" r:id="rId18" xr:uid="{F06237A8-E640-4E7E-A082-F2BC2BED78EC}"/>
+    <hyperlink ref="B48" r:id="rId19" xr:uid="{C888DAC6-3711-4670-8D7A-1B1812FD9651}"/>
+    <hyperlink ref="B49" r:id="rId20" xr:uid="{F152199A-3B33-4E8B-9569-E765B514FC06}"/>
+    <hyperlink ref="B50" r:id="rId21" xr:uid="{DD2B24B0-7A83-4DCC-AC66-9C9155CCD483}"/>
+    <hyperlink ref="B51" r:id="rId22" xr:uid="{BD28DC85-8833-44B6-8313-3339DE544490}"/>
+    <hyperlink ref="B52" r:id="rId23" xr:uid="{E0893EE2-FF1A-4406-9A68-BA70A3F8982A}"/>
+    <hyperlink ref="B53" r:id="rId24" xr:uid="{98FBBBC8-DA13-494D-9B3F-0F3011E83B45}"/>
+    <hyperlink ref="B54" r:id="rId25" xr:uid="{370A45EC-0A63-4FBF-A223-BB15B7BD86CD}"/>
+    <hyperlink ref="B55" r:id="rId26" xr:uid="{0E64F1BC-136E-4C53-BA5B-E4E4D9C919B2}"/>
+    <hyperlink ref="B56" r:id="rId27" xr:uid="{7710D6BE-BF89-4C5B-89F1-BD06F88903A8}"/>
+    <hyperlink ref="B57" r:id="rId28" xr:uid="{E3DDE7D2-1DD4-44D7-ADE5-573203DB93D8}"/>
+    <hyperlink ref="B58" r:id="rId29" xr:uid="{589ECA41-F587-4D3B-A69E-3B7AD1E3EFD8}"/>
+    <hyperlink ref="B59" r:id="rId30" xr:uid="{CC67BC7A-C346-4F44-A276-4037765AE3B4}"/>
+    <hyperlink ref="B60" r:id="rId31" xr:uid="{0D4C934A-D7C4-4111-8F0C-D59E353A315B}"/>
+    <hyperlink ref="B61" r:id="rId32" xr:uid="{34B788CD-0A7B-4753-9B50-4A3EE812BBD9}"/>
+    <hyperlink ref="B62" r:id="rId33" xr:uid="{ED8362E0-BC13-45E2-A761-4D84990C9E8F}"/>
+    <hyperlink ref="B63" r:id="rId34" xr:uid="{E5176278-5720-445B-AE58-05F5647541B1}"/>
+    <hyperlink ref="B64" r:id="rId35" xr:uid="{FC0F185E-57D9-4323-AFC2-AE2480A9CCBE}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId4"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId36"/>
 </worksheet>
 </file>
 
@@ -6070,18 +7150,18 @@
   <sheetPr>
     <tabColor theme="6" tint="0.79998168889431442"/>
   </sheetPr>
-  <dimension ref="A1:L32"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <dimension ref="A1:L64"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="53.86328125" customWidth="1"/>
-    <col min="2" max="2" width="11.54296875" customWidth="1"/>
-    <col min="3" max="3" width="36.2265625" customWidth="1"/>
-    <col min="4" max="4" width="50.2265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.53125" customWidth="1"/>
+    <col min="3" max="3" width="36.19921875" customWidth="1"/>
+    <col min="4" max="4" width="50.19921875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="62" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="93.6328125" customWidth="1"/>
+    <col min="12" max="12" width="93.59765625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.45">
       <c r="A1" s="16" t="s">
         <v>9</v>
       </c>
@@ -6098,14 +7178,14 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:12" ht="32" x14ac:dyDescent="0.75">
-      <c r="A2" t="s">
+    <row r="2" spans="1:12" ht="31.5" x14ac:dyDescent="0.45">
+      <c r="A2" s="58" t="s">
         <v>408</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>77</v>
-      </c>
-      <c r="C2" s="11" t="s">
+        <v>14</v>
+      </c>
+      <c r="C2" s="6" t="s">
         <v>29</v>
       </c>
       <c r="D2" s="43" t="s">
@@ -6115,15 +7195,15 @@
         <v>472</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="48" x14ac:dyDescent="0.75">
+    <row r="3" spans="1:12" ht="47.25" x14ac:dyDescent="0.45">
       <c r="A3" s="26" t="s">
         <v>437</v>
       </c>
       <c r="B3" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C3" s="11" t="s">
-        <v>29</v>
+      <c r="C3" s="6" t="s">
+        <v>485</v>
       </c>
       <c r="D3" s="43" t="s">
         <v>428</v>
@@ -6134,15 +7214,15 @@
       </c>
       <c r="L3" s="43"/>
     </row>
-    <row r="4" spans="1:12" ht="48" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:12" ht="47.25" x14ac:dyDescent="0.45">
       <c r="A4" s="26" t="s">
         <v>438</v>
       </c>
       <c r="B4" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C4" s="11" t="s">
-        <v>29</v>
+      <c r="C4" s="6" t="s">
+        <v>485</v>
       </c>
       <c r="D4" s="43" t="s">
         <v>429</v>
@@ -6153,15 +7233,15 @@
       </c>
       <c r="L4" s="43"/>
     </row>
-    <row r="5" spans="1:12" ht="48" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:12" ht="47.25" x14ac:dyDescent="0.45">
       <c r="A5" s="26" t="s">
         <v>439</v>
       </c>
       <c r="B5" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C5" s="11" t="s">
-        <v>29</v>
+      <c r="C5" s="6" t="s">
+        <v>485</v>
       </c>
       <c r="D5" s="43" t="s">
         <v>430</v>
@@ -6173,15 +7253,15 @@
       <c r="H5" s="3"/>
       <c r="L5" s="43"/>
     </row>
-    <row r="6" spans="1:12" ht="48" x14ac:dyDescent="0.75">
+    <row r="6" spans="1:12" ht="47.25" x14ac:dyDescent="0.45">
       <c r="A6" s="26" t="s">
         <v>440</v>
       </c>
       <c r="B6" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C6" s="11" t="s">
-        <v>29</v>
+      <c r="C6" s="6" t="s">
+        <v>485</v>
       </c>
       <c r="D6" s="48" t="s">
         <v>431</v>
@@ -6192,15 +7272,15 @@
       </c>
       <c r="L6" s="43"/>
     </row>
-    <row r="7" spans="1:12" ht="48" x14ac:dyDescent="0.75">
+    <row r="7" spans="1:12" ht="47.25" x14ac:dyDescent="0.45">
       <c r="A7" s="32" t="s">
         <v>441</v>
       </c>
       <c r="B7" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C7" s="11" t="s">
-        <v>29</v>
+      <c r="C7" s="6" t="s">
+        <v>485</v>
       </c>
       <c r="D7" s="43" t="s">
         <v>489</v>
@@ -6211,15 +7291,15 @@
       </c>
       <c r="L7" s="43"/>
     </row>
-    <row r="8" spans="1:12" ht="48" x14ac:dyDescent="0.75">
+    <row r="8" spans="1:12" ht="47.25" x14ac:dyDescent="0.45">
       <c r="A8" s="33" t="s">
         <v>442</v>
       </c>
       <c r="B8" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C8" s="11" t="s">
-        <v>29</v>
+      <c r="C8" s="6" t="s">
+        <v>485</v>
       </c>
       <c r="D8" s="43" t="s">
         <v>432</v>
@@ -6230,15 +7310,15 @@
       </c>
       <c r="L8" s="43"/>
     </row>
-    <row r="9" spans="1:12" ht="48" x14ac:dyDescent="0.75">
+    <row r="9" spans="1:12" ht="47.25" x14ac:dyDescent="0.45">
       <c r="A9" s="26" t="s">
         <v>443</v>
       </c>
       <c r="B9" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C9" s="11" t="s">
-        <v>29</v>
+      <c r="C9" s="6" t="s">
+        <v>485</v>
       </c>
       <c r="D9" s="43" t="s">
         <v>490</v>
@@ -6249,15 +7329,15 @@
       </c>
       <c r="L9" s="43"/>
     </row>
-    <row r="10" spans="1:12" ht="48" x14ac:dyDescent="0.75">
+    <row r="10" spans="1:12" ht="47.25" x14ac:dyDescent="0.45">
       <c r="A10" s="26" t="s">
         <v>444</v>
       </c>
       <c r="B10" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C10" s="11" t="s">
-        <v>29</v>
+      <c r="C10" s="6" t="s">
+        <v>485</v>
       </c>
       <c r="D10" s="43" t="s">
         <v>433</v>
@@ -6268,15 +7348,15 @@
       </c>
       <c r="L10" s="43"/>
     </row>
-    <row r="11" spans="1:12" ht="48" x14ac:dyDescent="0.75">
+    <row r="11" spans="1:12" ht="47.25" x14ac:dyDescent="0.45">
       <c r="A11" s="26" t="s">
         <v>445</v>
       </c>
       <c r="B11" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C11" s="11" t="s">
-        <v>29</v>
+      <c r="C11" s="6" t="s">
+        <v>485</v>
       </c>
       <c r="D11" s="43" t="s">
         <v>434</v>
@@ -6287,15 +7367,15 @@
       </c>
       <c r="L11" s="43"/>
     </row>
-    <row r="12" spans="1:12" ht="48" x14ac:dyDescent="0.75">
+    <row r="12" spans="1:12" ht="47.25" x14ac:dyDescent="0.45">
       <c r="A12" s="26" t="s">
         <v>446</v>
       </c>
       <c r="B12" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C12" s="11" t="s">
-        <v>29</v>
+      <c r="C12" s="6" t="s">
+        <v>485</v>
       </c>
       <c r="D12" s="43" t="s">
         <v>435</v>
@@ -6306,15 +7386,15 @@
       </c>
       <c r="L12" s="43"/>
     </row>
-    <row r="13" spans="1:12" ht="48" x14ac:dyDescent="0.75">
+    <row r="13" spans="1:12" ht="47.25" x14ac:dyDescent="0.45">
       <c r="A13" s="26" t="s">
         <v>447</v>
       </c>
       <c r="B13" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C13" s="11" t="s">
-        <v>29</v>
+      <c r="C13" s="6" t="s">
+        <v>485</v>
       </c>
       <c r="D13" s="43" t="s">
         <v>436</v>
@@ -6325,15 +7405,15 @@
       </c>
       <c r="L13" s="43"/>
     </row>
-    <row r="14" spans="1:12" ht="48" x14ac:dyDescent="0.75">
+    <row r="14" spans="1:12" ht="47.25" x14ac:dyDescent="0.45">
       <c r="A14" s="26" t="s">
         <v>448</v>
       </c>
       <c r="B14" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C14" s="11" t="s">
-        <v>29</v>
+      <c r="C14" s="6" t="s">
+        <v>485</v>
       </c>
       <c r="D14" s="44" t="s">
         <v>427</v>
@@ -6343,15 +7423,15 @@
         <v>% of people with Cases of Gastrointestinal diseases - Cases of disease prevalence per 100.000 inhabitants, per district, for each of the causes considered as relatable to the project</v>
       </c>
     </row>
-    <row r="15" spans="1:12" ht="48" x14ac:dyDescent="0.75">
+    <row r="15" spans="1:12" ht="47.25" x14ac:dyDescent="0.45">
       <c r="A15" s="26" t="s">
         <v>449</v>
       </c>
       <c r="B15" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C15" s="11" t="s">
-        <v>29</v>
+      <c r="C15" s="6" t="s">
+        <v>485</v>
       </c>
       <c r="D15" s="45" t="s">
         <v>409</v>
@@ -6361,15 +7441,15 @@
         <v>% of people with long-term disease - Cases of disease prevalence per 100.000 inhabitants, per district, for each of the causes considered as relatable to the project</v>
       </c>
     </row>
-    <row r="16" spans="1:12" ht="48" x14ac:dyDescent="0.75">
+    <row r="16" spans="1:12" ht="47.25" x14ac:dyDescent="0.45">
       <c r="A16" s="26" t="s">
         <v>450</v>
       </c>
       <c r="B16" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C16" s="11" t="s">
-        <v>29</v>
+      <c r="C16" s="6" t="s">
+        <v>485</v>
       </c>
       <c r="D16" s="45" t="s">
         <v>410</v>
@@ -6379,15 +7459,15 @@
         <v>% of people without  long-term disease - Cases of disease prevalence per 100.000 inhabitants, per district, for each of the causes considered as relatable to the project</v>
       </c>
     </row>
-    <row r="17" spans="1:5" ht="48" x14ac:dyDescent="0.75">
+    <row r="17" spans="1:5" ht="47.25" x14ac:dyDescent="0.45">
       <c r="A17" s="26" t="s">
         <v>451</v>
       </c>
       <c r="B17" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C17" s="11" t="s">
-        <v>29</v>
+      <c r="C17" s="6" t="s">
+        <v>485</v>
       </c>
       <c r="D17" s="47" t="s">
         <v>411</v>
@@ -6397,15 +7477,15 @@
         <v>% of people with BMI &lt;18,5 - Cases of disease prevalence per 100.000 inhabitants, per district, for each of the causes considered as relatable to the project</v>
       </c>
     </row>
-    <row r="18" spans="1:5" ht="48" x14ac:dyDescent="0.75">
+    <row r="18" spans="1:5" ht="47.25" x14ac:dyDescent="0.45">
       <c r="A18" s="26" t="s">
         <v>452</v>
       </c>
       <c r="B18" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C18" s="11" t="s">
-        <v>29</v>
+      <c r="C18" s="6" t="s">
+        <v>485</v>
       </c>
       <c r="D18" s="47" t="s">
         <v>412</v>
@@ -6415,15 +7495,15 @@
         <v>% of people with BMI 18,5-24,9 - Cases of disease prevalence per 100.000 inhabitants, per district, for each of the causes considered as relatable to the project</v>
       </c>
     </row>
-    <row r="19" spans="1:5" ht="48" x14ac:dyDescent="0.75">
+    <row r="19" spans="1:5" ht="47.25" x14ac:dyDescent="0.45">
       <c r="A19" s="26" t="s">
         <v>453</v>
       </c>
       <c r="B19" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C19" s="11" t="s">
-        <v>29</v>
+      <c r="C19" s="6" t="s">
+        <v>485</v>
       </c>
       <c r="D19" s="47" t="s">
         <v>413</v>
@@ -6433,15 +7513,15 @@
         <v>% of people with BMI 25-29,9 - Cases of disease prevalence per 100.000 inhabitants, per district, for each of the causes considered as relatable to the project</v>
       </c>
     </row>
-    <row r="20" spans="1:5" ht="48" x14ac:dyDescent="0.75">
+    <row r="20" spans="1:5" ht="47.25" x14ac:dyDescent="0.45">
       <c r="A20" s="26" t="s">
         <v>454</v>
       </c>
       <c r="B20" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C20" s="11" t="s">
-        <v>29</v>
+      <c r="C20" s="6" t="s">
+        <v>485</v>
       </c>
       <c r="D20" s="47" t="s">
         <v>414</v>
@@ -6451,15 +7531,15 @@
         <v>% of people with BMI =&gt;30 - Cases of disease prevalence per 100.000 inhabitants, per district, for each of the causes considered as relatable to the project</v>
       </c>
     </row>
-    <row r="21" spans="1:5" ht="64" x14ac:dyDescent="0.75">
+    <row r="21" spans="1:5" ht="47.25" x14ac:dyDescent="0.45">
       <c r="A21" s="49" t="s">
         <v>455</v>
       </c>
       <c r="B21" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C21" s="11" t="s">
-        <v>29</v>
+      <c r="C21" s="6" t="s">
+        <v>485</v>
       </c>
       <c r="D21" s="45" t="s">
         <v>415</v>
@@ -6469,15 +7549,15 @@
         <v>% of people that have or have had Diabetes, COPD or Cardiovascular disease - Cases of disease prevalence per 100.000 inhabitants, per district, for each of the causes considered as relatable to the project</v>
       </c>
     </row>
-    <row r="22" spans="1:5" ht="64" x14ac:dyDescent="0.75">
+    <row r="22" spans="1:5" ht="47.25" x14ac:dyDescent="0.45">
       <c r="A22" s="49" t="s">
         <v>456</v>
       </c>
       <c r="B22" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C22" s="11" t="s">
-        <v>29</v>
+      <c r="C22" s="6" t="s">
+        <v>485</v>
       </c>
       <c r="D22" s="45" t="s">
         <v>416</v>
@@ -6487,15 +7567,15 @@
         <v>% of people that do not have Diabetes, COPD or Cardiovascular disease - Cases of disease prevalence per 100.000 inhabitants, per district, for each of the causes considered as relatable to the project</v>
       </c>
     </row>
-    <row r="23" spans="1:5" ht="48" x14ac:dyDescent="0.75">
+    <row r="23" spans="1:5" ht="47.25" x14ac:dyDescent="0.45">
       <c r="A23" s="49" t="s">
         <v>457</v>
       </c>
       <c r="B23" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C23" s="11" t="s">
-        <v>29</v>
+      <c r="C23" s="6" t="s">
+        <v>485</v>
       </c>
       <c r="D23" s="45" t="s">
         <v>417</v>
@@ -6505,15 +7585,15 @@
         <v>% of people experience with mental health issues - Cases of disease prevalence per 100.000 inhabitants, per district, for each of the causes considered as relatable to the project</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="48" x14ac:dyDescent="0.75">
+    <row r="24" spans="1:5" ht="47.25" x14ac:dyDescent="0.45">
       <c r="A24" s="49" t="s">
         <v>458</v>
       </c>
       <c r="B24" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C24" s="11" t="s">
-        <v>29</v>
+      <c r="C24" s="6" t="s">
+        <v>485</v>
       </c>
       <c r="D24" s="46" t="s">
         <v>418</v>
@@ -6523,15 +7603,15 @@
         <v>% of people with Borrelia Burgdoferi - Cases of disease prevalence per 100.000 inhabitants, per district, for each of the causes considered as relatable to the project</v>
       </c>
     </row>
-    <row r="25" spans="1:5" ht="48" x14ac:dyDescent="0.75">
+    <row r="25" spans="1:5" ht="47.25" x14ac:dyDescent="0.45">
       <c r="A25" s="26" t="s">
         <v>459</v>
       </c>
       <c r="B25" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C25" s="11" t="s">
-        <v>29</v>
+      <c r="C25" s="6" t="s">
+        <v>485</v>
       </c>
       <c r="D25" s="46" t="s">
         <v>419</v>
@@ -6541,15 +7621,15 @@
         <v>% of people with Campylobacter - Cases of disease prevalence per 100.000 inhabitants, per district, for each of the causes considered as relatable to the project</v>
       </c>
     </row>
-    <row r="26" spans="1:5" ht="48" x14ac:dyDescent="0.75">
+    <row r="26" spans="1:5" ht="47.25" x14ac:dyDescent="0.45">
       <c r="A26" s="26" t="s">
         <v>460</v>
       </c>
       <c r="B26" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C26" s="11" t="s">
-        <v>29</v>
+      <c r="C26" s="6" t="s">
+        <v>485</v>
       </c>
       <c r="D26" s="46" t="s">
         <v>420</v>
@@ -6559,15 +7639,15 @@
         <v>% of people with Chlamydia Psittaci - Cases of disease prevalence per 100.000 inhabitants, per district, for each of the causes considered as relatable to the project</v>
       </c>
     </row>
-    <row r="27" spans="1:5" ht="48" x14ac:dyDescent="0.75">
+    <row r="27" spans="1:5" ht="47.25" x14ac:dyDescent="0.45">
       <c r="A27" s="26" t="s">
         <v>461</v>
       </c>
       <c r="B27" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C27" s="11" t="s">
-        <v>29</v>
+      <c r="C27" s="6" t="s">
+        <v>485</v>
       </c>
       <c r="D27" s="46" t="s">
         <v>421</v>
@@ -6577,15 +7657,15 @@
         <v>% of people with Cryptosporidium - Cases of disease prevalence per 100.000 inhabitants, per district, for each of the causes considered as relatable to the project</v>
       </c>
     </row>
-    <row r="28" spans="1:5" ht="48" x14ac:dyDescent="0.75">
+    <row r="28" spans="1:5" ht="47.25" x14ac:dyDescent="0.45">
       <c r="A28" s="26" t="s">
         <v>462</v>
       </c>
       <c r="B28" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C28" s="11" t="s">
-        <v>29</v>
+      <c r="C28" s="6" t="s">
+        <v>485</v>
       </c>
       <c r="D28" s="46" t="s">
         <v>422</v>
@@ -6595,15 +7675,15 @@
         <v>% of people with Entamoeba histolytica - Cases of disease prevalence per 100.000 inhabitants, per district, for each of the causes considered as relatable to the project</v>
       </c>
     </row>
-    <row r="29" spans="1:5" ht="48" x14ac:dyDescent="0.75">
+    <row r="29" spans="1:5" ht="47.25" x14ac:dyDescent="0.45">
       <c r="A29" s="32" t="s">
         <v>463</v>
       </c>
       <c r="B29" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C29" s="11" t="s">
-        <v>29</v>
+      <c r="C29" s="6" t="s">
+        <v>485</v>
       </c>
       <c r="D29" s="46" t="s">
         <v>423</v>
@@ -6613,15 +7693,15 @@
         <v>% of people with Escherichia Coli - Cases of disease prevalence per 100.000 inhabitants, per district, for each of the causes considered as relatable to the project</v>
       </c>
     </row>
-    <row r="30" spans="1:5" ht="48" x14ac:dyDescent="0.75">
+    <row r="30" spans="1:5" ht="47.25" x14ac:dyDescent="0.45">
       <c r="A30" s="33" t="s">
         <v>464</v>
       </c>
       <c r="B30" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C30" s="11" t="s">
-        <v>29</v>
+      <c r="C30" s="6" t="s">
+        <v>485</v>
       </c>
       <c r="D30" s="46" t="s">
         <v>424</v>
@@ -6631,15 +7711,15 @@
         <v>% of people with Giarda - Cases of disease prevalence per 100.000 inhabitants, per district, for each of the causes considered as relatable to the project</v>
       </c>
     </row>
-    <row r="31" spans="1:5" ht="48" x14ac:dyDescent="0.75">
+    <row r="31" spans="1:5" ht="47.25" x14ac:dyDescent="0.45">
       <c r="A31" s="26" t="s">
         <v>465</v>
       </c>
       <c r="B31" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C31" s="11" t="s">
-        <v>29</v>
+      <c r="C31" s="6" t="s">
+        <v>485</v>
       </c>
       <c r="D31" s="46" t="s">
         <v>425</v>
@@ -6649,15 +7729,15 @@
         <v>% of people with Salmonella - Cases of disease prevalence per 100.000 inhabitants, per district, for each of the causes considered as relatable to the project</v>
       </c>
     </row>
-    <row r="32" spans="1:5" ht="48" x14ac:dyDescent="0.75">
+    <row r="32" spans="1:5" ht="47.25" x14ac:dyDescent="0.45">
       <c r="A32" s="26" t="s">
         <v>466</v>
       </c>
       <c r="B32" s="6" t="s">
         <v>14</v>
       </c>
-      <c r="C32" s="11" t="s">
-        <v>29</v>
+      <c r="C32" s="6" t="s">
+        <v>485</v>
       </c>
       <c r="D32" s="46" t="s">
         <v>426</v>
@@ -6667,9 +7747,574 @@
         <v>% of people with Yersinia enterocolitica - Cases of disease prevalence per 100.000 inhabitants, per district, for each of the causes considered as relatable to the project</v>
       </c>
     </row>
+    <row r="33" spans="1:8" ht="31.5" x14ac:dyDescent="0.45">
+      <c r="A33" s="57" t="s">
+        <v>493</v>
+      </c>
+      <c r="B33" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C33" s="6" t="s">
+        <v>29</v>
+      </c>
+      <c r="D33" s="43" t="s">
+        <v>538</v>
+      </c>
+      <c r="E33" s="43" t="s">
+        <v>539</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" ht="15.75" x14ac:dyDescent="0.45">
+      <c r="A34" s="56" t="s">
+        <v>494</v>
+      </c>
+      <c r="B34" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C34" s="6" t="s">
+        <v>485</v>
+      </c>
+      <c r="D34" s="51" t="s">
+        <v>508</v>
+      </c>
+      <c r="E34" s="59" t="str">
+        <f>D34&amp;" - Cases per 100.000 inhabitants, per district, for each of the causes considered as relatable to the project"</f>
+        <v>% of deaths due to TBC - Cases per 100.000 inhabitants, per district, for each of the causes considered as relatable to the project</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" ht="31.5" x14ac:dyDescent="0.45">
+      <c r="A35" s="56" t="s">
+        <v>495</v>
+      </c>
+      <c r="B35" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C35" s="6" t="s">
+        <v>485</v>
+      </c>
+      <c r="D35" s="51" t="s">
+        <v>509</v>
+      </c>
+      <c r="E35" s="59" t="str">
+        <f t="shared" ref="E35:E47" si="1">D35&amp;" - Cases per 100.000 inhabitants, per district, for each of the causes considered as relatable to the project"</f>
+        <v>% of deaths due to Viral Hepatitis - Cases per 100.000 inhabitants, per district, for each of the causes considered as relatable to the project</v>
+      </c>
+      <c r="H35" s="53"/>
+    </row>
+    <row r="36" spans="1:8" ht="31.5" x14ac:dyDescent="0.45">
+      <c r="A36" s="56" t="s">
+        <v>496</v>
+      </c>
+      <c r="B36" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C36" s="6" t="s">
+        <v>485</v>
+      </c>
+      <c r="D36" s="51" t="s">
+        <v>510</v>
+      </c>
+      <c r="E36" s="59" t="str">
+        <f t="shared" si="1"/>
+        <v>% of deaths due to infective and parasitic diseases - Cases per 100.000 inhabitants, per district, for each of the causes considered as relatable to the project</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" ht="31.5" x14ac:dyDescent="0.45">
+      <c r="A37" s="56" t="s">
+        <v>497</v>
+      </c>
+      <c r="B37" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C37" s="6" t="s">
+        <v>485</v>
+      </c>
+      <c r="D37" s="51" t="s">
+        <v>511</v>
+      </c>
+      <c r="E37" s="59" t="str">
+        <f t="shared" si="1"/>
+        <v>% of deaths due to diseases of the blood and hematopoietic organs - Cases per 100.000 inhabitants, per district, for each of the causes considered as relatable to the project</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" ht="31.5" x14ac:dyDescent="0.45">
+      <c r="A38" s="56" t="s">
+        <v>498</v>
+      </c>
+      <c r="B38" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C38" s="6" t="s">
+        <v>485</v>
+      </c>
+      <c r="D38" s="51" t="s">
+        <v>512</v>
+      </c>
+      <c r="E38" s="59" t="str">
+        <f t="shared" si="1"/>
+        <v>% of deaths due to Diabetes Mellitus - Cases per 100.000 inhabitants, per district, for each of the causes considered as relatable to the project</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" ht="31.5" x14ac:dyDescent="0.45">
+      <c r="A39" s="56" t="s">
+        <v>499</v>
+      </c>
+      <c r="B39" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C39" s="6" t="s">
+        <v>485</v>
+      </c>
+      <c r="D39" s="51" t="s">
+        <v>513</v>
+      </c>
+      <c r="E39" s="59" t="str">
+        <f t="shared" si="1"/>
+        <v>% of deaths due to endocrine, nutritional and metabolic diseases - Cases per 100.000 inhabitants, per district, for each of the causes considered as relatable to the project</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" ht="31.5" x14ac:dyDescent="0.45">
+      <c r="A40" s="56" t="s">
+        <v>500</v>
+      </c>
+      <c r="B40" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C40" s="6" t="s">
+        <v>485</v>
+      </c>
+      <c r="D40" s="52" t="s">
+        <v>514</v>
+      </c>
+      <c r="E40" s="59" t="str">
+        <f t="shared" si="1"/>
+        <v>% of deaths due to ischemic diseases of the heart - Cases per 100.000 inhabitants, per district, for each of the causes considered as relatable to the project</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" ht="31.5" x14ac:dyDescent="0.45">
+      <c r="A41" s="56" t="s">
+        <v>501</v>
+      </c>
+      <c r="B41" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C41" s="6" t="s">
+        <v>485</v>
+      </c>
+      <c r="D41" s="52" t="s">
+        <v>515</v>
+      </c>
+      <c r="E41" s="59" t="str">
+        <f t="shared" si="1"/>
+        <v>% of deaths due to other diseases of the heart - Cases per 100.000 inhabitants, per district, for each of the causes considered as relatable to the project</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" ht="31.5" x14ac:dyDescent="0.45">
+      <c r="A42" s="56" t="s">
+        <v>502</v>
+      </c>
+      <c r="B42" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C42" s="6" t="s">
+        <v>485</v>
+      </c>
+      <c r="D42" s="52" t="s">
+        <v>516</v>
+      </c>
+      <c r="E42" s="59" t="str">
+        <f t="shared" si="1"/>
+        <v>% of deaths due to other diseases of the circulatory system  - Cases per 100.000 inhabitants, per district, for each of the causes considered as relatable to the project</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" ht="31.5" x14ac:dyDescent="0.45">
+      <c r="A43" s="56" t="s">
+        <v>503</v>
+      </c>
+      <c r="B43" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C43" s="6" t="s">
+        <v>485</v>
+      </c>
+      <c r="D43" s="51" t="s">
+        <v>517</v>
+      </c>
+      <c r="E43" s="59" t="str">
+        <f t="shared" si="1"/>
+        <v>% of deaths due to Pneumonia - Cases per 100.000 inhabitants, per district, for each of the causes considered as relatable to the project</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" ht="31.5" x14ac:dyDescent="0.45">
+      <c r="A44" s="56" t="s">
+        <v>504</v>
+      </c>
+      <c r="B44" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C44" s="6" t="s">
+        <v>485</v>
+      </c>
+      <c r="D44" s="52" t="s">
+        <v>518</v>
+      </c>
+      <c r="E44" s="59" t="str">
+        <f t="shared" si="1"/>
+        <v>% of deaths due to chronic diseases of the lower respiratory tract - Cases per 100.000 inhabitants, per district, for each of the causes considered as relatable to the project</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" ht="31.5" x14ac:dyDescent="0.45">
+      <c r="A45" s="56" t="s">
+        <v>505</v>
+      </c>
+      <c r="B45" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C45" s="6" t="s">
+        <v>485</v>
+      </c>
+      <c r="D45" s="52" t="s">
+        <v>519</v>
+      </c>
+      <c r="E45" s="59" t="str">
+        <f t="shared" si="1"/>
+        <v>% of deaths due to other diseases of the respiratory system - Cases per 100.000 inhabitants, per district, for each of the causes considered as relatable to the project</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" ht="31.5" x14ac:dyDescent="0.45">
+      <c r="A46" s="56" t="s">
+        <v>506</v>
+      </c>
+      <c r="B46" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C46" s="6" t="s">
+        <v>485</v>
+      </c>
+      <c r="D46" s="52" t="s">
+        <v>520</v>
+      </c>
+      <c r="E46" s="59" t="str">
+        <f t="shared" si="1"/>
+        <v>% of deaths due to diseases of the skin and subcutaneous tissue - Cases per 100.000 inhabitants, per district, for each of the causes considered as relatable to the project</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" ht="31.5" x14ac:dyDescent="0.45">
+      <c r="A47" s="56" t="s">
+        <v>507</v>
+      </c>
+      <c r="B47" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C47" s="6" t="s">
+        <v>485</v>
+      </c>
+      <c r="D47" s="51" t="s">
+        <v>521</v>
+      </c>
+      <c r="E47" s="59" t="str">
+        <f t="shared" si="1"/>
+        <v>% of deaths due to accidental poisoning - Cases per 100.000 inhabitants, per district, for each of the causes considered as relatable to the project</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" ht="47.25" x14ac:dyDescent="0.45">
+      <c r="A48" s="56" t="s">
+        <v>531</v>
+      </c>
+      <c r="B48" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C48" s="6" t="s">
+        <v>485</v>
+      </c>
+      <c r="D48" t="s">
+        <v>528</v>
+      </c>
+      <c r="E48" s="59" t="str">
+        <f>D48&amp;" - Cases per 100.000 inhabitants, per parish for each of the causes considered as relatable to the project"</f>
+        <v>% of deaths due to Malignant Tumors - Cases per 100.000 inhabitants, per parish for each of the causes considered as relatable to the project</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" ht="47.25" x14ac:dyDescent="0.45">
+      <c r="A49" s="56" t="s">
+        <v>532</v>
+      </c>
+      <c r="B49" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C49" s="6" t="s">
+        <v>485</v>
+      </c>
+      <c r="D49" t="s">
+        <v>529</v>
+      </c>
+      <c r="E49" s="59" t="str">
+        <f t="shared" ref="E49:E50" si="2">D49&amp;" - Cases per 100.000 inhabitants, per parish for each of the causes considered as relatable to the project"</f>
+        <v>% of deaths due to Healthcare-Sensitive Causes  - Cases per 100.000 inhabitants, per parish for each of the causes considered as relatable to the project</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" ht="31.5" x14ac:dyDescent="0.45">
+      <c r="A50" s="56" t="s">
+        <v>533</v>
+      </c>
+      <c r="B50" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C50" s="6" t="s">
+        <v>485</v>
+      </c>
+      <c r="D50" t="s">
+        <v>530</v>
+      </c>
+      <c r="E50" s="59" t="str">
+        <f t="shared" si="2"/>
+        <v>% of Excess Mortality in Winter - Cases per 100.000 inhabitants, per parish for each of the causes considered as relatable to the project</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" ht="31.5" x14ac:dyDescent="0.45">
+      <c r="A51" s="56" t="s">
+        <v>534</v>
+      </c>
+      <c r="B51" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C51" s="6" t="s">
+        <v>485</v>
+      </c>
+      <c r="D51" s="55" t="s">
+        <v>526</v>
+      </c>
+      <c r="E51" s="59" t="str">
+        <f>D51&amp;" - Cases per 100.000 inhabitants, per borough for each of the causes considered as relatable to the project"</f>
+        <v>% of deaths due to all causes - Cases per 100.000 inhabitants, per borough for each of the causes considered as relatable to the project</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" ht="31.5" x14ac:dyDescent="0.45">
+      <c r="A52" s="56" t="s">
+        <v>535</v>
+      </c>
+      <c r="B52" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C52" s="6" t="s">
+        <v>485</v>
+      </c>
+      <c r="D52" s="55" t="s">
+        <v>522</v>
+      </c>
+      <c r="E52" s="59" t="str">
+        <f t="shared" ref="E52:E56" si="3">D52&amp;" - Cases per 100.000 inhabitants, per borough for each of the causes considered as relatable to the project"</f>
+        <v>% of deaths due to cancer - Cases per 100.000 inhabitants, per borough for each of the causes considered as relatable to the project</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" ht="31.5" x14ac:dyDescent="0.45">
+      <c r="A53" s="56" t="s">
+        <v>536</v>
+      </c>
+      <c r="B53" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C53" s="6" t="s">
+        <v>485</v>
+      </c>
+      <c r="D53" s="55" t="s">
+        <v>527</v>
+      </c>
+      <c r="E53" s="59" t="str">
+        <f t="shared" si="3"/>
+        <v>% of deaths due to diabetes - Cases per 100.000 inhabitants, per borough for each of the causes considered as relatable to the project</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" ht="47.25" x14ac:dyDescent="0.45">
+      <c r="A54" s="56" t="s">
+        <v>555</v>
+      </c>
+      <c r="B54" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C54" s="6" t="s">
+        <v>485</v>
+      </c>
+      <c r="D54" s="55" t="s">
+        <v>523</v>
+      </c>
+      <c r="E54" s="59" t="str">
+        <f t="shared" si="3"/>
+        <v>% of deaths due to cardiovascular disease - Cases per 100.000 inhabitants, per borough for each of the causes considered as relatable to the project</v>
+      </c>
+      <c r="F54" s="54"/>
+    </row>
+    <row r="55" spans="1:6" ht="47.25" x14ac:dyDescent="0.45">
+      <c r="A55" s="56" t="s">
+        <v>556</v>
+      </c>
+      <c r="B55" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C55" s="6" t="s">
+        <v>485</v>
+      </c>
+      <c r="D55" s="55" t="s">
+        <v>524</v>
+      </c>
+      <c r="E55" s="59" t="str">
+        <f t="shared" si="3"/>
+        <v>% of deaths due to respiratory disease - Cases per 100.000 inhabitants, per borough for each of the causes considered as relatable to the project</v>
+      </c>
+    </row>
+    <row r="56" spans="1:6" ht="47.25" x14ac:dyDescent="0.45">
+      <c r="A56" s="56" t="s">
+        <v>537</v>
+      </c>
+      <c r="B56" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C56" s="6" t="s">
+        <v>485</v>
+      </c>
+      <c r="D56" s="55" t="s">
+        <v>525</v>
+      </c>
+      <c r="E56" s="59" t="str">
+        <f t="shared" si="3"/>
+        <v>% of deaths due to COPD and lung cancer - Cases per 100.000 inhabitants, per borough for each of the causes considered as relatable to the project</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A57" s="60" t="s">
+        <v>554</v>
+      </c>
+      <c r="B57" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C57" s="6" t="s">
+        <v>485</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A58" s="61" t="s">
+        <v>557</v>
+      </c>
+      <c r="B58" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C58" s="6" t="s">
+        <v>485</v>
+      </c>
+      <c r="D58" t="s">
+        <v>540</v>
+      </c>
+      <c r="E58" t="s">
+        <v>541</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" ht="42.75" x14ac:dyDescent="0.45">
+      <c r="A59" s="61" t="s">
+        <v>558</v>
+      </c>
+      <c r="B59" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C59" s="6" t="s">
+        <v>485</v>
+      </c>
+      <c r="D59" s="5" t="s">
+        <v>542</v>
+      </c>
+      <c r="E59" s="5" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" ht="15.75" x14ac:dyDescent="0.45">
+      <c r="A60" s="62" t="s">
+        <v>561</v>
+      </c>
+      <c r="B60" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C60" s="6" t="s">
+        <v>485</v>
+      </c>
+      <c r="D60" t="s">
+        <v>544</v>
+      </c>
+      <c r="E60" t="s">
+        <v>545</v>
+      </c>
+      <c r="F60" s="53"/>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A61" s="61" t="s">
+        <v>559</v>
+      </c>
+      <c r="B61" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C61" s="6" t="s">
+        <v>485</v>
+      </c>
+      <c r="D61" t="s">
+        <v>546</v>
+      </c>
+      <c r="E61" t="s">
+        <v>547</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A62" s="61" t="s">
+        <v>560</v>
+      </c>
+      <c r="B62" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C62" s="6" t="s">
+        <v>485</v>
+      </c>
+      <c r="D62" t="s">
+        <v>548</v>
+      </c>
+      <c r="E62" t="s">
+        <v>549</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.45">
+      <c r="A63" s="61" t="s">
+        <v>562</v>
+      </c>
+      <c r="B63" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C63" s="6" t="s">
+        <v>485</v>
+      </c>
+      <c r="D63" t="s">
+        <v>550</v>
+      </c>
+      <c r="E63" t="s">
+        <v>551</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" ht="42.75" x14ac:dyDescent="0.45">
+      <c r="A64" s="61" t="s">
+        <v>563</v>
+      </c>
+      <c r="B64" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C64" s="6" t="s">
+        <v>485</v>
+      </c>
+      <c r="D64" s="5" t="s">
+        <v>552</v>
+      </c>
+      <c r="E64" s="5" t="s">
+        <v>553</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -6679,19 +8324,19 @@
     <tabColor theme="7" tint="0.59999389629810485"/>
   </sheetPr>
   <dimension ref="A1:H63"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="58.08984375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="58.06640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="71.86328125" customWidth="1"/>
-    <col min="3" max="3" width="76.76953125" style="5" customWidth="1"/>
-    <col min="4" max="4" width="44.54296875" style="5" customWidth="1"/>
-    <col min="5" max="5" width="36.2265625" customWidth="1"/>
+    <col min="3" max="3" width="76.796875" style="5" customWidth="1"/>
+    <col min="4" max="4" width="44.53125" style="5" customWidth="1"/>
+    <col min="5" max="5" width="36.19921875" customWidth="1"/>
     <col min="6" max="6" width="22" customWidth="1"/>
-    <col min="7" max="7" width="11.08984375" customWidth="1"/>
-    <col min="8" max="8" width="37.54296875" style="5" customWidth="1"/>
+    <col min="7" max="7" width="11.06640625" customWidth="1"/>
+    <col min="8" max="8" width="37.53125" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="14" customFormat="1" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:8" s="14" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
@@ -6717,7 +8362,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.75">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A2" s="7" t="str">
         <f>"http://hl7.eu/fhir/ig/oah/StructureDefinition/"&amp;LogicalModels!$A$2</f>
         <v>http://hl7.eu/fhir/ig/oah/StructureDefinition/IndicatorsOah</v>
@@ -6742,7 +8387,7 @@
       </c>
       <c r="H2" s="8"/>
     </row>
-    <row r="3" spans="1:8" ht="29.5" x14ac:dyDescent="0.75">
+    <row r="3" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A3" s="7" t="str">
         <f>"http://hl7.eu/fhir/ig/oah/StructureDefinition/"&amp;LogicalModels!$A$2</f>
         <v>http://hl7.eu/fhir/ig/oah/StructureDefinition/IndicatorsOah</v>
@@ -6772,7 +8417,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A4" s="7" t="str">
         <f>"http://hl7.eu/fhir/ig/oah/StructureDefinition/"&amp;LogicalModels!$A$2</f>
         <v>http://hl7.eu/fhir/ig/oah/StructureDefinition/IndicatorsOah</v>
@@ -6799,7 +8444,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A5" s="7" t="str">
         <f>"http://hl7.eu/fhir/ig/oah/StructureDefinition/"&amp;LogicalModels!$A$2</f>
         <v>http://hl7.eu/fhir/ig/oah/StructureDefinition/IndicatorsOah</v>
@@ -6826,7 +8471,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="6" spans="1:8" ht="44.25" x14ac:dyDescent="0.75">
+    <row r="6" spans="1:8" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A6" s="7" t="str">
         <f>"http://hl7.eu/fhir/ig/oah/StructureDefinition/"&amp;LogicalModels!$A$2</f>
         <v>http://hl7.eu/fhir/ig/oah/StructureDefinition/IndicatorsOah</v>
@@ -6853,7 +8498,7 @@
         <v>192</v>
       </c>
     </row>
-    <row r="7" spans="1:8" ht="44.25" x14ac:dyDescent="0.75">
+    <row r="7" spans="1:8" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A7" s="7" t="str">
         <f>"http://hl7.eu/fhir/ig/oah/StructureDefinition/"&amp;LogicalModels!$A$2</f>
         <v>http://hl7.eu/fhir/ig/oah/StructureDefinition/IndicatorsOah</v>
@@ -6880,7 +8525,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.75">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A8" s="7" t="str">
         <f>"http://hl7.eu/fhir/ig/oah/StructureDefinition/"&amp;LogicalModels!$A$2</f>
         <v>http://hl7.eu/fhir/ig/oah/StructureDefinition/IndicatorsOah</v>
@@ -6907,7 +8552,7 @@
         <v>170</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.75">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A9" s="7" t="str">
         <f>"http://hl7.eu/fhir/ig/oah/StructureDefinition/"&amp;LogicalModels!$A$2</f>
         <v>http://hl7.eu/fhir/ig/oah/StructureDefinition/IndicatorsOah</v>
@@ -6932,7 +8577,7 @@
       </c>
       <c r="H9" s="8"/>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.75">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A10" s="7" t="str">
         <f>"http://hl7.eu/fhir/ig/oah/StructureDefinition/"&amp;LogicalModels!$A$2</f>
         <v>http://hl7.eu/fhir/ig/oah/StructureDefinition/IndicatorsOah</v>
@@ -6959,7 +8604,7 @@
         <v>171</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.75">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A11" s="7" t="str">
         <f>"http://hl7.eu/fhir/ig/oah/StructureDefinition/"&amp;LogicalModels!$A$2</f>
         <v>http://hl7.eu/fhir/ig/oah/StructureDefinition/IndicatorsOah</v>
@@ -6986,7 +8631,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.75">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A12" s="7" t="str">
         <f>"http://hl7.eu/fhir/ig/oah/StructureDefinition/"&amp;LogicalModels!$A$2</f>
         <v>http://hl7.eu/fhir/ig/oah/StructureDefinition/IndicatorsOah</v>
@@ -7013,7 +8658,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.75">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A13" s="7" t="str">
         <f>"http://hl7.eu/fhir/ig/oah/StructureDefinition/"&amp;LogicalModels!$A$2</f>
         <v>http://hl7.eu/fhir/ig/oah/StructureDefinition/IndicatorsOah</v>
@@ -7038,7 +8683,7 @@
       </c>
       <c r="H13" s="8"/>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.75">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A14" s="7" t="str">
         <f>"http://hl7.eu/fhir/ig/oah/StructureDefinition/"&amp;LogicalModels!$A$2</f>
         <v>http://hl7.eu/fhir/ig/oah/StructureDefinition/IndicatorsOah</v>
@@ -7065,7 +8710,7 @@
         <v>174</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.75">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A15" s="7" t="str">
         <f>"http://hl7.eu/fhir/ig/oah/StructureDefinition/"&amp;LogicalModels!$A$2</f>
         <v>http://hl7.eu/fhir/ig/oah/StructureDefinition/IndicatorsOah</v>
@@ -7092,7 +8737,7 @@
         <v>175</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.75">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A16" s="7" t="str">
         <f>"http://hl7.eu/fhir/ig/oah/StructureDefinition/"&amp;LogicalModels!$A$2</f>
         <v>http://hl7.eu/fhir/ig/oah/StructureDefinition/IndicatorsOah</v>
@@ -7119,7 +8764,7 @@
         <v>176</v>
       </c>
     </row>
-    <row r="17" spans="1:8" ht="29.5" x14ac:dyDescent="0.75">
+    <row r="17" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A17" s="7" t="str">
         <f>"http://hl7.eu/fhir/ig/oah/StructureDefinition/"&amp;LogicalModels!$A$2</f>
         <v>http://hl7.eu/fhir/ig/oah/StructureDefinition/IndicatorsOah</v>
@@ -7146,7 +8791,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.75">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A18" s="7" t="str">
         <f>"http://hl7.eu/fhir/ig/oah/StructureDefinition/"&amp;LogicalModels!$A$2</f>
         <v>http://hl7.eu/fhir/ig/oah/StructureDefinition/IndicatorsOah</v>
@@ -7173,7 +8818,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.75">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A19" s="7" t="str">
         <f>"http://hl7.eu/fhir/ig/oah/StructureDefinition/"&amp;LogicalModels!$A$2</f>
         <v>http://hl7.eu/fhir/ig/oah/StructureDefinition/IndicatorsOah</v>
@@ -7200,7 +8845,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.75">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A20" s="7" t="str">
         <f>"http://hl7.eu/fhir/ig/oah/StructureDefinition/"&amp;LogicalModels!$A$2</f>
         <v>http://hl7.eu/fhir/ig/oah/StructureDefinition/IndicatorsOah</v>
@@ -7227,7 +8872,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="21" spans="1:8" ht="29.5" x14ac:dyDescent="0.75">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A21" s="7" t="str">
         <f>"http://hl7.eu/fhir/ig/oah/StructureDefinition/"&amp;LogicalModels!$A$2</f>
         <v>http://hl7.eu/fhir/ig/oah/StructureDefinition/IndicatorsOah</v>
@@ -7254,7 +8899,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.75">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A22" s="7" t="str">
         <f>"http://hl7.eu/fhir/ig/oah/StructureDefinition/"&amp;LogicalModels!$A$2</f>
         <v>http://hl7.eu/fhir/ig/oah/StructureDefinition/IndicatorsOah</v>
@@ -7281,7 +8926,7 @@
         <v>182</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.75">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A23" s="7" t="str">
         <f>"http://hl7.eu/fhir/ig/oah/StructureDefinition/"&amp;LogicalModels!$A$2</f>
         <v>http://hl7.eu/fhir/ig/oah/StructureDefinition/IndicatorsOah</v>
@@ -7308,7 +8953,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.75">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A24" s="7" t="str">
         <f>"http://hl7.eu/fhir/ig/oah/StructureDefinition/"&amp;LogicalModels!$A$2</f>
         <v>http://hl7.eu/fhir/ig/oah/StructureDefinition/IndicatorsOah</v>
@@ -7333,7 +8978,7 @@
       </c>
       <c r="H24" s="8"/>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.75">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A25" s="7" t="str">
         <f>"http://hl7.eu/fhir/ig/oah/StructureDefinition/"&amp;LogicalModels!$A$2</f>
         <v>http://hl7.eu/fhir/ig/oah/StructureDefinition/IndicatorsOah</v>
@@ -7360,7 +9005,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.75">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A26" s="7" t="str">
         <f>"http://hl7.eu/fhir/ig/oah/StructureDefinition/"&amp;LogicalModels!$A$2</f>
         <v>http://hl7.eu/fhir/ig/oah/StructureDefinition/IndicatorsOah</v>
@@ -7387,7 +9032,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="27" spans="1:8" ht="29.5" x14ac:dyDescent="0.75">
+    <row r="27" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A27" s="7" t="str">
         <f>"http://hl7.eu/fhir/ig/oah/StructureDefinition/"&amp;LogicalModels!$A$2</f>
         <v>http://hl7.eu/fhir/ig/oah/StructureDefinition/IndicatorsOah</v>
@@ -7414,7 +9059,7 @@
         <v>186</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.75">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A28" s="7" t="str">
         <f>"http://hl7.eu/fhir/ig/oah/StructureDefinition/"&amp;LogicalModels!$A$2</f>
         <v>http://hl7.eu/fhir/ig/oah/StructureDefinition/IndicatorsOah</v>
@@ -7441,7 +9086,7 @@
         <v>187</v>
       </c>
     </row>
-    <row r="29" spans="1:8" ht="29.5" x14ac:dyDescent="0.75">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A29" s="7" t="str">
         <f>"http://hl7.eu/fhir/ig/oah/StructureDefinition/"&amp;LogicalModels!$A$2</f>
         <v>http://hl7.eu/fhir/ig/oah/StructureDefinition/IndicatorsOah</v>
@@ -7468,7 +9113,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.75">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A30" s="7" t="str">
         <f>"http://hl7.eu/fhir/ig/oah/StructureDefinition/"&amp;LogicalModels!$A$2</f>
         <v>http://hl7.eu/fhir/ig/oah/StructureDefinition/IndicatorsOah</v>
@@ -7495,7 +9140,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.75">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A31" s="7" t="str">
         <f>"http://hl7.eu/fhir/ig/oah/StructureDefinition/"&amp;LogicalModels!$A$2</f>
         <v>http://hl7.eu/fhir/ig/oah/StructureDefinition/IndicatorsOah</v>
@@ -7522,7 +9167,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.75">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A32" s="7" t="str">
         <f>"http://hl7.eu/fhir/ig/oah/StructureDefinition/"&amp;LogicalModels!$A$2</f>
         <v>http://hl7.eu/fhir/ig/oah/StructureDefinition/IndicatorsOah</v>
@@ -7549,7 +9194,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.75">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A33" s="7" t="str">
         <f>"http://hl7.eu/fhir/ig/oah/StructureDefinition/"&amp;LogicalModels!$A$2</f>
         <v>http://hl7.eu/fhir/ig/oah/StructureDefinition/IndicatorsOah</v>
@@ -7576,7 +9221,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.75">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A34" s="7" t="str">
         <f>"http://hl7.eu/fhir/ig/oah/StructureDefinition/"&amp;LogicalModels!$A$2</f>
         <v>http://hl7.eu/fhir/ig/oah/StructureDefinition/IndicatorsOah</v>
@@ -7603,7 +9248,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.75">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A35" s="7" t="str">
         <f>"http://hl7.eu/fhir/ig/oah/StructureDefinition/"&amp;LogicalModels!$A$2</f>
         <v>http://hl7.eu/fhir/ig/oah/StructureDefinition/IndicatorsOah</v>
@@ -7630,7 +9275,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.75">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A36" s="7" t="str">
         <f>"http://hl7.eu/fhir/ig/oah/StructureDefinition/"&amp;LogicalModels!$A$2</f>
         <v>http://hl7.eu/fhir/ig/oah/StructureDefinition/IndicatorsOah</v>
@@ -7657,7 +9302,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.75">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A37" s="7"/>
       <c r="B37" s="7" t="s">
         <v>103</v>
@@ -7681,7 +9326,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.75">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A38" s="7" t="str">
         <f>"http://hl7.eu/fhir/ig/oah/StructureDefinition/"&amp;LogicalModels!$A$2</f>
         <v>http://hl7.eu/fhir/ig/oah/StructureDefinition/IndicatorsOah</v>
@@ -7708,7 +9353,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.75">
+    <row r="39" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A39" s="7"/>
       <c r="B39" s="7" t="s">
         <v>103</v>
@@ -7732,7 +9377,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.75">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A40" s="7" t="str">
         <f>"http://hl7.eu/fhir/ig/oah/StructureDefinition/"&amp;LogicalModels!$A$2</f>
         <v>http://hl7.eu/fhir/ig/oah/StructureDefinition/IndicatorsOah</v>
@@ -7759,7 +9404,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.75">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A41" s="7" t="str">
         <f>"http://hl7.eu/fhir/ig/oah/StructureDefinition/"&amp;LogicalModels!$A$2</f>
         <v>http://hl7.eu/fhir/ig/oah/StructureDefinition/IndicatorsOah</v>
@@ -7786,7 +9431,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.75">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A42" s="7" t="str">
         <f>"http://hl7.eu/fhir/ig/oah/StructureDefinition/"&amp;LogicalModels!$A$2</f>
         <v>http://hl7.eu/fhir/ig/oah/StructureDefinition/IndicatorsOah</v>
@@ -7813,7 +9458,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.75">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A43" s="7" t="str">
         <f>"http://hl7.eu/fhir/ig/oah/StructureDefinition/"&amp;LogicalModels!$A$2</f>
         <v>http://hl7.eu/fhir/ig/oah/StructureDefinition/IndicatorsOah</v>
@@ -7840,7 +9485,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.75">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A44" s="7" t="str">
         <f>"http://hl7.eu/fhir/ig/oah/StructureDefinition/"&amp;LogicalModels!$A$2</f>
         <v>http://hl7.eu/fhir/ig/oah/StructureDefinition/IndicatorsOah</v>
@@ -7867,7 +9512,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.75">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A45" s="7" t="str">
         <f>"http://hl7.eu/fhir/ig/oah/StructureDefinition/"&amp;LogicalModels!$A$2</f>
         <v>http://hl7.eu/fhir/ig/oah/StructureDefinition/IndicatorsOah</v>
@@ -7894,7 +9539,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.75">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A46" s="7" t="str">
         <f>"http://hl7.eu/fhir/ig/oah/StructureDefinition/"&amp;LogicalModels!$A$2</f>
         <v>http://hl7.eu/fhir/ig/oah/StructureDefinition/IndicatorsOah</v>
@@ -7921,7 +9566,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.75">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A47" s="7" t="str">
         <f>"http://hl7.eu/fhir/ig/oah/StructureDefinition/"&amp;LogicalModels!$A$2</f>
         <v>http://hl7.eu/fhir/ig/oah/StructureDefinition/IndicatorsOah</v>
@@ -7948,7 +9593,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.75">
+    <row r="48" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A48" s="7" t="str">
         <f>"http://hl7.eu/fhir/ig/oah/StructureDefinition/"&amp;LogicalModels!$A$2</f>
         <v>http://hl7.eu/fhir/ig/oah/StructureDefinition/IndicatorsOah</v>
@@ -7975,7 +9620,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.75">
+    <row r="49" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A49" s="7" t="str">
         <f>"http://hl7.eu/fhir/ig/oah/StructureDefinition/"&amp;LogicalModels!$A$2</f>
         <v>http://hl7.eu/fhir/ig/oah/StructureDefinition/IndicatorsOah</v>
@@ -8002,7 +9647,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.75">
+    <row r="50" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A50" s="7" t="str">
         <f>"http://hl7.eu/fhir/ig/oah/StructureDefinition/"&amp;LogicalModels!$A$2</f>
         <v>http://hl7.eu/fhir/ig/oah/StructureDefinition/IndicatorsOah</v>
@@ -8029,7 +9674,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.75">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A51" s="7" t="str">
         <f>"http://hl7.eu/fhir/ig/oah/StructureDefinition/"&amp;LogicalModels!$A$2</f>
         <v>http://hl7.eu/fhir/ig/oah/StructureDefinition/IndicatorsOah</v>
@@ -8056,7 +9701,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.75">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A52" s="7" t="str">
         <f>"http://hl7.eu/fhir/ig/oah/StructureDefinition/"&amp;LogicalModels!$A$2</f>
         <v>http://hl7.eu/fhir/ig/oah/StructureDefinition/IndicatorsOah</v>
@@ -8083,7 +9728,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.75">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A53" s="7" t="str">
         <f>"http://hl7.eu/fhir/ig/oah/StructureDefinition/"&amp;LogicalModels!$A$2</f>
         <v>http://hl7.eu/fhir/ig/oah/StructureDefinition/IndicatorsOah</v>
@@ -8110,7 +9755,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.75">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A54" s="7" t="str">
         <f>"http://hl7.eu/fhir/ig/oah/StructureDefinition/"&amp;LogicalModels!$A$2</f>
         <v>http://hl7.eu/fhir/ig/oah/StructureDefinition/IndicatorsOah</v>
@@ -8137,7 +9782,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.75">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A55" s="7" t="str">
         <f>"http://hl7.eu/fhir/ig/oah/StructureDefinition/"&amp;LogicalModels!$A$2</f>
         <v>http://hl7.eu/fhir/ig/oah/StructureDefinition/IndicatorsOah</v>
@@ -8164,7 +9809,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.75">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A56" s="7" t="str">
         <f>"http://hl7.eu/fhir/ig/oah/StructureDefinition/"&amp;LogicalModels!$A$2</f>
         <v>http://hl7.eu/fhir/ig/oah/StructureDefinition/IndicatorsOah</v>
@@ -8191,7 +9836,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.75">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A57" s="7" t="str">
         <f>"http://hl7.eu/fhir/ig/oah/StructureDefinition/"&amp;LogicalModels!$A$2</f>
         <v>http://hl7.eu/fhir/ig/oah/StructureDefinition/IndicatorsOah</v>
@@ -8218,7 +9863,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.75">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A58" s="7" t="str">
         <f>"http://hl7.eu/fhir/ig/oah/StructureDefinition/"&amp;LogicalModels!$A$2</f>
         <v>http://hl7.eu/fhir/ig/oah/StructureDefinition/IndicatorsOah</v>
@@ -8245,7 +9890,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.75">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A59" s="7" t="str">
         <f>"http://hl7.eu/fhir/ig/oah/StructureDefinition/"&amp;LogicalModels!$A$2</f>
         <v>http://hl7.eu/fhir/ig/oah/StructureDefinition/IndicatorsOah</v>
@@ -8272,7 +9917,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.75">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A60" s="7" t="str">
         <f>"http://hl7.eu/fhir/ig/oah/StructureDefinition/"&amp;LogicalModels!$A$2</f>
         <v>http://hl7.eu/fhir/ig/oah/StructureDefinition/IndicatorsOah</v>
@@ -8299,7 +9944,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.75">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A61" s="7" t="str">
         <f>"http://hl7.eu/fhir/ig/oah/StructureDefinition/"&amp;LogicalModels!$A$2</f>
         <v>http://hl7.eu/fhir/ig/oah/StructureDefinition/IndicatorsOah</v>
@@ -8326,7 +9971,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.75">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A62" s="7" t="str">
         <f>"http://hl7.eu/fhir/ig/oah/StructureDefinition/"&amp;LogicalModels!$A$2</f>
         <v>http://hl7.eu/fhir/ig/oah/StructureDefinition/IndicatorsOah</v>
@@ -8353,7 +9998,7 @@
         <v>190</v>
       </c>
     </row>
-    <row r="63" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.75">
+    <row r="63" spans="1:8" s="3" customFormat="1" x14ac:dyDescent="0.45">
       <c r="C63" s="42"/>
       <c r="D63" s="42"/>
       <c r="H63" s="42"/>
@@ -8375,16 +10020,16 @@
     <tabColor theme="6" tint="0.79998168889431442"/>
   </sheetPr>
   <dimension ref="A1:E62"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="53.86328125" customWidth="1"/>
-    <col min="2" max="2" width="11.54296875" customWidth="1"/>
-    <col min="3" max="3" width="36.2265625" customWidth="1"/>
-    <col min="4" max="4" width="50.2265625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.53125" customWidth="1"/>
+    <col min="3" max="3" width="36.19921875" customWidth="1"/>
+    <col min="4" max="4" width="50.19921875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="62" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A1" s="16" t="s">
         <v>9</v>
       </c>
@@ -8401,7 +10046,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="44.25" x14ac:dyDescent="0.75">
+    <row r="2" spans="1:5" ht="42.75" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>69</v>
       </c>
@@ -8418,7 +10063,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="29.5" x14ac:dyDescent="0.75">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A3" s="26" t="s">
         <v>71</v>
       </c>
@@ -8435,7 +10080,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="29.5" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:5" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A4" s="26" t="s">
         <v>72</v>
       </c>
@@ -8452,7 +10097,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A5" s="26" t="s">
         <v>73</v>
       </c>
@@ -8469,7 +10114,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A6" s="26" t="s">
         <v>74</v>
       </c>
@@ -8486,7 +10131,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A7" s="32" t="s">
         <v>75</v>
       </c>
@@ -8503,7 +10148,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A8" s="33" t="s">
         <v>76</v>
       </c>
@@ -8520,7 +10165,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="103.25" x14ac:dyDescent="0.75">
+    <row r="9" spans="1:5" ht="99.75" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>70</v>
       </c>
@@ -8537,7 +10182,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="29.5" x14ac:dyDescent="0.75">
+    <row r="10" spans="1:5" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A10" s="20" t="s">
         <v>78</v>
       </c>
@@ -8554,7 +10199,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="29.5" x14ac:dyDescent="0.75">
+    <row r="11" spans="1:5" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A11" s="20" t="s">
         <v>79</v>
       </c>
@@ -8571,7 +10216,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A12" s="20" t="s">
         <v>80</v>
       </c>
@@ -8588,7 +10233,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="118" x14ac:dyDescent="0.75">
+    <row r="13" spans="1:5" ht="114" x14ac:dyDescent="0.45">
       <c r="A13" s="20" t="s">
         <v>81</v>
       </c>
@@ -8605,7 +10250,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A14" s="21" t="s">
         <v>82</v>
       </c>
@@ -8622,7 +10267,7 @@
         <v>45</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A15" s="21" t="s">
         <v>83</v>
       </c>
@@ -8639,7 +10284,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A16" s="21" t="s">
         <v>84</v>
       </c>
@@ -8656,7 +10301,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A17" s="21" t="s">
         <v>85</v>
       </c>
@@ -8673,7 +10318,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A18" s="21" t="s">
         <v>86</v>
       </c>
@@ -8690,7 +10335,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A19" s="21" t="s">
         <v>87</v>
       </c>
@@ -8707,7 +10352,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A20" s="21" t="s">
         <v>88</v>
       </c>
@@ -8724,7 +10369,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A21" s="21" t="s">
         <v>89</v>
       </c>
@@ -8741,7 +10386,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A22" s="21" t="s">
         <v>90</v>
       </c>
@@ -8758,7 +10403,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A23" s="21" t="s">
         <v>91</v>
       </c>
@@ -8775,7 +10420,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="24" spans="1:5" ht="88.5" x14ac:dyDescent="0.75">
+    <row r="24" spans="1:5" ht="71.25" x14ac:dyDescent="0.45">
       <c r="A24" s="21" t="s">
         <v>92</v>
       </c>
@@ -8792,7 +10437,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A25" s="22" t="s">
         <v>93</v>
       </c>
@@ -8809,7 +10454,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A26" s="22" t="s">
         <v>94</v>
       </c>
@@ -8826,7 +10471,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A27" s="22" t="s">
         <v>95</v>
       </c>
@@ -8843,7 +10488,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A28" s="22" t="s">
         <v>96</v>
       </c>
@@ -8860,7 +10505,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A29" s="22" t="s">
         <v>97</v>
       </c>
@@ -8877,7 +10522,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A30" s="22" t="s">
         <v>98</v>
       </c>
@@ -8894,7 +10539,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A31" s="22" t="s">
         <v>99</v>
       </c>
@@ -8911,7 +10556,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="32" spans="1:5" ht="29.5" x14ac:dyDescent="0.75">
+    <row r="32" spans="1:5" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A32" s="21" t="s">
         <v>315</v>
       </c>
@@ -8928,7 +10573,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A33" s="22" t="s">
         <v>318</v>
       </c>
@@ -8945,7 +10590,7 @@
         <v>320</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A34" s="22" t="s">
         <v>321</v>
       </c>
@@ -8962,7 +10607,7 @@
         <v>323</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A35" s="22" t="s">
         <v>324</v>
       </c>
@@ -8979,7 +10624,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A36" s="22" t="s">
         <v>327</v>
       </c>
@@ -8996,7 +10641,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A37" s="22" t="s">
         <v>339</v>
       </c>
@@ -9013,7 +10658,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A38" s="22" t="s">
         <v>330</v>
       </c>
@@ -9030,7 +10675,7 @@
         <v>332</v>
       </c>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A39" s="22" t="s">
         <v>336</v>
       </c>
@@ -9047,7 +10692,7 @@
         <v>338</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A40" s="22" t="s">
         <v>333</v>
       </c>
@@ -9064,7 +10709,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A41" s="22" t="s">
         <v>342</v>
       </c>
@@ -9081,7 +10726,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A42" s="22" t="s">
         <v>343</v>
       </c>
@@ -9098,7 +10743,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A43" s="22" t="s">
         <v>344</v>
       </c>
@@ -9115,7 +10760,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A44" s="22" t="s">
         <v>345</v>
       </c>
@@ -9132,7 +10777,7 @@
         <v>367</v>
       </c>
     </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A45" s="22" t="s">
         <v>346</v>
       </c>
@@ -9149,7 +10794,7 @@
         <v>368</v>
       </c>
     </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A46" s="22" t="s">
         <v>347</v>
       </c>
@@ -9166,7 +10811,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A47" s="22" t="s">
         <v>348</v>
       </c>
@@ -9183,7 +10828,7 @@
         <v>370</v>
       </c>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A48" s="22" t="s">
         <v>349</v>
       </c>
@@ -9200,7 +10845,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A49" s="22" t="s">
         <v>350</v>
       </c>
@@ -9217,7 +10862,7 @@
         <v>372</v>
       </c>
     </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A50" s="22" t="s">
         <v>351</v>
       </c>
@@ -9234,7 +10879,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A51" s="22" t="s">
         <v>352</v>
       </c>
@@ -9251,7 +10896,7 @@
         <v>374</v>
       </c>
     </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A52" s="22" t="s">
         <v>353</v>
       </c>
@@ -9268,7 +10913,7 @@
         <v>375</v>
       </c>
     </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A53" s="22" t="s">
         <v>407</v>
       </c>
@@ -9285,7 +10930,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A54" s="22" t="s">
         <v>354</v>
       </c>
@@ -9302,7 +10947,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A55" s="22" t="s">
         <v>355</v>
       </c>
@@ -9319,7 +10964,7 @@
         <v>378</v>
       </c>
     </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A56" s="22" t="s">
         <v>356</v>
       </c>
@@ -9336,7 +10981,7 @@
         <v>379</v>
       </c>
     </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A57" s="22" t="s">
         <v>357</v>
       </c>
@@ -9353,7 +10998,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A58" s="22" t="s">
         <v>358</v>
       </c>
@@ -9370,7 +11015,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A59" s="22" t="s">
         <v>359</v>
       </c>
@@ -9387,7 +11032,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A60" s="22" t="s">
         <v>360</v>
       </c>
@@ -9404,7 +11049,7 @@
         <v>383</v>
       </c>
     </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A61" s="22" t="s">
         <v>361</v>
       </c>
@@ -9421,7 +11066,7 @@
         <v>384</v>
       </c>
     </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A62" s="22" t="s">
         <v>362</v>
       </c>
@@ -9449,19 +11094,19 @@
     <tabColor theme="7" tint="0.59999389629810485"/>
   </sheetPr>
   <dimension ref="A1:H16"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="58.08984375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="58.06640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="71.86328125" customWidth="1"/>
-    <col min="3" max="3" width="24.76953125" style="5" customWidth="1"/>
-    <col min="4" max="4" width="31.2265625" style="5" customWidth="1"/>
-    <col min="5" max="5" width="31.2265625" customWidth="1"/>
+    <col min="3" max="3" width="24.796875" style="5" customWidth="1"/>
+    <col min="4" max="4" width="31.19921875" style="5" customWidth="1"/>
+    <col min="5" max="5" width="31.19921875" customWidth="1"/>
     <col min="6" max="6" width="22" customWidth="1"/>
-    <col min="7" max="7" width="11.08984375" customWidth="1"/>
-    <col min="8" max="8" width="37.54296875" style="5" customWidth="1"/>
+    <col min="7" max="7" width="11.06640625" customWidth="1"/>
+    <col min="8" max="8" width="37.53125" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="14" customFormat="1" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:8" s="14" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
@@ -9487,7 +11132,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="29.5" x14ac:dyDescent="0.75">
+    <row r="2" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A2" s="7" t="str">
         <f>"http://hl7.eu/fhir/ig/oah/StructureDefinition/"&amp;LogicalModels!$A$8</f>
         <v>http://hl7.eu/fhir/ig/oah/StructureDefinition/HealthMeasure</v>
@@ -9514,7 +11159,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.75">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A3" s="7" t="str">
         <f>"http://hl7.eu/fhir/ig/oah/StructureDefinition/"&amp;LogicalModels!$A$8</f>
         <v>http://hl7.eu/fhir/ig/oah/StructureDefinition/HealthMeasure</v>
@@ -9539,7 +11184,7 @@
       </c>
       <c r="H3" s="8"/>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A4" s="7" t="str">
         <f>"http://hl7.eu/fhir/ig/oah/StructureDefinition/"&amp;LogicalModels!$A$8</f>
         <v>http://hl7.eu/fhir/ig/oah/StructureDefinition/HealthMeasure</v>
@@ -9567,7 +11212,7 @@
       </c>
       <c r="H4" s="8"/>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A5" s="7" t="str">
         <f>"http://hl7.eu/fhir/ig/oah/StructureDefinition/"&amp;LogicalModels!$A$8</f>
         <v>http://hl7.eu/fhir/ig/oah/StructureDefinition/HealthMeasure</v>
@@ -9595,7 +11240,7 @@
       </c>
       <c r="H5" s="8"/>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.75">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A6" s="7" t="str">
         <f>"http://hl7.eu/fhir/ig/oah/StructureDefinition/"&amp;LogicalModels!$A$8</f>
         <v>http://hl7.eu/fhir/ig/oah/StructureDefinition/HealthMeasure</v>
@@ -9623,7 +11268,7 @@
       </c>
       <c r="H6" s="8"/>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.75">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A7" s="7" t="str">
         <f>"http://hl7.eu/fhir/ig/oah/StructureDefinition/"&amp;LogicalModels!$A$8</f>
         <v>http://hl7.eu/fhir/ig/oah/StructureDefinition/HealthMeasure</v>
@@ -9650,7 +11295,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.75">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A8" s="7" t="str">
         <f>"http://hl7.eu/fhir/ig/oah/StructureDefinition/"&amp;LogicalModels!$A$8</f>
         <v>http://hl7.eu/fhir/ig/oah/StructureDefinition/HealthMeasure</v>
@@ -9675,7 +11320,7 @@
       </c>
       <c r="H8" s="8"/>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.75">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A9" s="7" t="str">
         <f>"http://hl7.eu/fhir/ig/oah/StructureDefinition/"&amp;LogicalModels!$A$8</f>
         <v>http://hl7.eu/fhir/ig/oah/StructureDefinition/HealthMeasure</v>
@@ -9698,7 +11343,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.75">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A10" s="7" t="str">
         <f>"http://hl7.eu/fhir/ig/oah/StructureDefinition/"&amp;LogicalModels!$A$8</f>
         <v>http://hl7.eu/fhir/ig/oah/StructureDefinition/HealthMeasure</v>
@@ -9721,7 +11366,7 @@
         <v>211</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.75">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A11" s="7" t="str">
         <f>"http://hl7.eu/fhir/ig/oah/StructureDefinition/"&amp;LogicalModels!$A$8</f>
         <v>http://hl7.eu/fhir/ig/oah/StructureDefinition/HealthMeasure</v>
@@ -9744,7 +11389,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.75">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A12" s="7" t="str">
         <f>"http://hl7.eu/fhir/ig/oah/StructureDefinition/"&amp;LogicalModels!$A$8</f>
         <v>http://hl7.eu/fhir/ig/oah/StructureDefinition/HealthMeasure</v>
@@ -9767,19 +11412,19 @@
         <v>211</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.75">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.45">
       <c r="C13"/>
       <c r="D13"/>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.75">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.45">
       <c r="C14"/>
       <c r="D14"/>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.75">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.45">
       <c r="C15"/>
       <c r="D15"/>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.75">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.45">
       <c r="C16"/>
       <c r="D16"/>
     </row>
@@ -9802,16 +11447,16 @@
     <tabColor theme="6" tint="0.79998168889431442"/>
   </sheetPr>
   <dimension ref="A1:E11"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="20.453125" customWidth="1"/>
-    <col min="2" max="2" width="11.54296875" customWidth="1"/>
+    <col min="1" max="1" width="20.46484375" customWidth="1"/>
+    <col min="2" max="2" width="11.53125" customWidth="1"/>
     <col min="3" max="3" width="33" customWidth="1"/>
-    <col min="4" max="4" width="23.31640625" customWidth="1"/>
-    <col min="5" max="5" width="35.08984375" style="5" customWidth="1"/>
+    <col min="4" max="4" width="23.33203125" customWidth="1"/>
+    <col min="5" max="5" width="35.06640625" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A1" s="16" t="s">
         <v>9</v>
       </c>
@@ -9828,7 +11473,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A2" s="8" t="s">
         <v>107</v>
       </c>
@@ -9845,7 +11490,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A3" s="8" t="s">
         <v>135</v>
       </c>
@@ -9862,7 +11507,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A4" s="8" t="s">
         <v>108</v>
       </c>
@@ -9879,7 +11524,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A5" s="8" t="s">
         <v>109</v>
       </c>
@@ -9896,7 +11541,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A6" s="8" t="s">
         <v>118</v>
       </c>
@@ -9913,7 +11558,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A7" s="8" t="s">
         <v>474</v>
       </c>
@@ -9930,7 +11575,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.75">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A8" s="8" t="s">
         <v>152</v>
       </c>
@@ -9947,7 +11592,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="29.5" x14ac:dyDescent="0.75">
+    <row r="9" spans="1:5" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A9" s="6" t="s">
         <v>141</v>
       </c>
@@ -9964,7 +11609,7 @@
         <v>477</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="29.5" x14ac:dyDescent="0.75">
+    <row r="10" spans="1:5" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A10" s="6" t="s">
         <v>149</v>
       </c>
@@ -9981,7 +11626,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="29.5" x14ac:dyDescent="0.75">
+    <row r="11" spans="1:5" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A11" s="8" t="s">
         <v>478</v>
       </c>
@@ -10009,19 +11654,19 @@
     <tabColor theme="7" tint="0.59999389629810485"/>
   </sheetPr>
   <dimension ref="A1:H8"/>
-  <sheetFormatPr defaultRowHeight="14.75" x14ac:dyDescent="0.75"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="58.08984375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="58.06640625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="71.86328125" customWidth="1"/>
-    <col min="3" max="3" width="24.76953125" style="5" customWidth="1"/>
-    <col min="4" max="4" width="31.2265625" style="5" customWidth="1"/>
-    <col min="5" max="5" width="31.2265625" customWidth="1"/>
+    <col min="3" max="3" width="24.796875" style="5" customWidth="1"/>
+    <col min="4" max="4" width="31.19921875" style="5" customWidth="1"/>
+    <col min="5" max="5" width="31.19921875" customWidth="1"/>
     <col min="6" max="6" width="22" customWidth="1"/>
-    <col min="7" max="7" width="11.08984375" customWidth="1"/>
-    <col min="8" max="8" width="37.54296875" style="5" customWidth="1"/>
+    <col min="7" max="7" width="11.06640625" customWidth="1"/>
+    <col min="8" max="8" width="37.53125" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" s="14" customFormat="1" x14ac:dyDescent="0.75">
+    <row r="1" spans="1:8" s="14" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
@@ -10047,7 +11692,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="2" spans="1:8" ht="29.5" x14ac:dyDescent="0.75">
+    <row r="2" spans="1:8" ht="28.5" x14ac:dyDescent="0.45">
       <c r="A2" s="7" t="str">
         <f>"http://hl7.eu/fhir/ig/oah/StructureDefinition/"&amp;LogicalModels!$A$3</f>
         <v>http://hl7.eu/fhir/ig/oah/StructureDefinition/SimpleIndicator</v>
@@ -10074,7 +11719,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.75">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A3" s="7" t="str">
         <f>"http://hl7.eu/fhir/ig/oah/StructureDefinition/"&amp;LogicalModels!$A$3</f>
         <v>http://hl7.eu/fhir/ig/oah/StructureDefinition/SimpleIndicator</v>
@@ -10099,7 +11744,7 @@
       </c>
       <c r="H3" s="8"/>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.75">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A4" s="7" t="str">
         <f>"http://hl7.eu/fhir/ig/oah/StructureDefinition/"&amp;LogicalModels!$A$3</f>
         <v>http://hl7.eu/fhir/ig/oah/StructureDefinition/SimpleIndicator</v>
@@ -10127,7 +11772,7 @@
       </c>
       <c r="H4" s="8"/>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.75">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A5" s="7" t="str">
         <f>"http://hl7.eu/fhir/ig/oah/StructureDefinition/"&amp;LogicalModels!$A$3</f>
         <v>http://hl7.eu/fhir/ig/oah/StructureDefinition/SimpleIndicator</v>
@@ -10155,7 +11800,7 @@
       </c>
       <c r="H5" s="8"/>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.75">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A6" s="7" t="str">
         <f>"http://hl7.eu/fhir/ig/oah/StructureDefinition/"&amp;LogicalModels!$A$3</f>
         <v>http://hl7.eu/fhir/ig/oah/StructureDefinition/SimpleIndicator</v>
@@ -10180,7 +11825,7 @@
       </c>
       <c r="H6" s="8"/>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.75">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A7" s="7" t="str">
         <f>"http://hl7.eu/fhir/ig/oah/StructureDefinition/"&amp;LogicalModels!$A$3</f>
         <v>http://hl7.eu/fhir/ig/oah/StructureDefinition/SimpleIndicator</v>
@@ -10207,7 +11852,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.75">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.45">
       <c r="A8" s="7" t="str">
         <f>"http://hl7.eu/fhir/ig/oah/StructureDefinition/"&amp;LogicalModels!$A$3</f>
         <v>http://hl7.eu/fhir/ig/oah/StructureDefinition/SimpleIndicator</v>

--- a/models-src/oah-models-and-maps.xlsx
+++ b/models-src/oah-models-and-maps.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\workspace\oah\models-src\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4561212D-6D29-488F-857E-9D760D31EABF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A9135FCD-67B7-48B8-A1E6-C0B0B9A70BE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-6510" yWindow="-21710" windowWidth="38620" windowHeight="21100" activeTab="2" xr2:uid="{FA01C668-562A-4AF9-BDB0-B212F14DE883}"/>
+    <workbookView xWindow="-6510" yWindow="-21710" windowWidth="38620" windowHeight="21100" activeTab="3" xr2:uid="{FA01C668-562A-4AF9-BDB0-B212F14DE883}"/>
   </bookViews>
   <sheets>
     <sheet name="ConceptMaps" sheetId="17" r:id="rId1"/>
@@ -56,7 +56,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1655" uniqueCount="564">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1656" uniqueCount="565">
   <si>
     <t>Group Source</t>
   </si>
@@ -1751,6 +1751,9 @@
   </si>
   <si>
     <t>hospitalization.avoidablePrimaryPrevention</t>
+  </si>
+  <si>
+    <t>Hospitalizations</t>
   </si>
 </sst>
 </file>
@@ -1994,7 +1997,7 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="63">
+  <cellXfs count="64">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -2124,12 +2127,15 @@
     <xf numFmtId="0" fontId="0" fillId="9" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="10" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="12" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="4" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Collegamento ipertestuale" xfId="1" builtinId="8"/>
@@ -2156,6 +2162,7 @@
   <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
     <xxl21:alternateUrls>
       <xxl21:absoluteUrl r:id="rId2"/>
+      <xxl21:relativeUrl r:id="rId3"/>
     </xxl21:alternateUrls>
     <sheetNames>
       <sheetName val="Hospital Discharge Report "/>
@@ -6913,9 +6920,9 @@
         <f>HealthIndicatorsOah!A57</f>
         <v>hospitalization</v>
       </c>
-      <c r="D57" s="8">
+      <c r="D57" s="8" t="str">
         <f>HealthIndicatorsOah!D57</f>
-        <v>0</v>
+        <v>Hospitalizations</v>
       </c>
       <c r="E57" s="8" t="s">
         <v>27</v>
@@ -8103,7 +8110,7 @@
         <v>522</v>
       </c>
       <c r="E52" s="59" t="str">
-        <f t="shared" ref="E52:E56" si="3">D52&amp;" - Cases per 100.000 inhabitants, per borough for each of the causes considered as relatable to the project"</f>
+        <f t="shared" ref="E52:E57" si="3">D52&amp;" - Cases per 100.000 inhabitants, per borough for each of the causes considered as relatable to the project"</f>
         <v>% of deaths due to cancer - Cases per 100.000 inhabitants, per borough for each of the causes considered as relatable to the project</v>
       </c>
     </row>
@@ -8180,7 +8187,7 @@
         <v>% of deaths due to COPD and lung cancer - Cases per 100.000 inhabitants, per borough for each of the causes considered as relatable to the project</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.45">
+    <row r="57" spans="1:6" ht="47.25" x14ac:dyDescent="0.45">
       <c r="A57" s="60" t="s">
         <v>554</v>
       </c>
@@ -8188,7 +8195,14 @@
         <v>14</v>
       </c>
       <c r="C57" s="6" t="s">
-        <v>485</v>
+        <v>29</v>
+      </c>
+      <c r="D57" s="63" t="s">
+        <v>564</v>
+      </c>
+      <c r="E57" s="59" t="str">
+        <f t="shared" si="3"/>
+        <v>Hospitalizations - Cases per 100.000 inhabitants, per borough for each of the causes considered as relatable to the project</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.45">
